--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,44 +1231,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139492</v>
+        <v>129139418</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>97533</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1278,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467077</v>
+        <v>467036</v>
       </c>
       <c r="R7" t="n">
-        <v>6858863</v>
+        <v>6858929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,36 +1343,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129139418</v>
+        <v>129139492</v>
       </c>
       <c r="B8" t="n">
-        <v>97528</v>
+        <v>98656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467036</v>
+        <v>467077</v>
       </c>
       <c r="R8" t="n">
-        <v>6858929</v>
+        <v>6858863</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,6 +1691,4041 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129175183</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79066</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>185</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>466875</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6859008</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129175597</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>466883</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6858994</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129175634</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78792</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>467082</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6859023</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129175025</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>467093</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6859264</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129175614</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>466857</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6858979</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Noterat läte.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129174816</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>467156</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6859054</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129175174</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79066</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>185</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>467140</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6859092</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129174925</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>466878</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6858977</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129175206</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79066</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>185</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>466900</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6858997</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129174937</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>466864</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6858963</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129175049</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>466848</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6858995</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129174881</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>467170</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6859051</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129175691</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>467064</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6859142</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129174865</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>467191</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6859075</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129175162</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80175</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>467175</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6859056</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129174848</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>467183</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6859065</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129174912</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>467130</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6859021</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129175199</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79066</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>185</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>466889</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6859006</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129174765</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>467126</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6859081</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129175673</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>467135</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6859085</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129175713</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79066</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>185</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>467077</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6858882</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129174795</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>467160</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6859063</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129174832</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>467161</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6859044</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129174783</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>467141</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6859072</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129175650</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78792</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>466895</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6858952</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129174896</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>467147</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6859035</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129175151</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57827</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>466858</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6859162</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129175792</v>
+      </c>
+      <c r="B38" t="n">
+        <v>92816</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>467058</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6858890</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129175680</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>467104</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6859032</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129175685</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>467096</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6859018</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129174718</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>467122</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6859101</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129175136</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>467042</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6858941</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129174751</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98656</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>467131</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6859085</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129175662</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78792</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>466918</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6858992</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129175069</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57723</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>466837</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6858989</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129139219</v>
       </c>
       <c r="B2" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129138843</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,36 +1231,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139418</v>
+        <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>97533</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1270,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467036</v>
+        <v>467077</v>
       </c>
       <c r="R7" t="n">
-        <v>6858929</v>
+        <v>6858863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,44 +1351,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129139492</v>
+        <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>98656</v>
+        <v>97536</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467077</v>
+        <v>467036</v>
       </c>
       <c r="R8" t="n">
-        <v>6858863</v>
+        <v>6858929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1466,7 @@
         <v>129139232</v>
       </c>
       <c r="B9" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>129175183</v>
       </c>
       <c r="B11" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,26 +1935,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R13" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2022,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,27 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R14" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2132,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,46 +2267,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174816</v>
+        <v>129175174</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>79067</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467140</v>
       </c>
       <c r="R16" t="n">
-        <v>6859054</v>
+        <v>6859092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,37 +2378,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129175174</v>
+        <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>79066</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467140</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6859092</v>
+        <v>6859054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2501,7 +2501,7 @@
         <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>129175206</v>
       </c>
       <c r="B19" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>129174937</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,38 +2841,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129175049</v>
+        <v>129174881</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2880,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466848</v>
+        <v>467170</v>
       </c>
       <c r="R21" t="n">
-        <v>6858995</v>
+        <v>6859051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,17 +2936,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2957,46 +2961,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174881</v>
+        <v>129175049</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +3000,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467170</v>
+        <v>466848</v>
       </c>
       <c r="R22" t="n">
-        <v>6859051</v>
+        <v>6858995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,13 +3048,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>129175691</v>
       </c>
       <c r="B23" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129174865</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>129175162</v>
       </c>
       <c r="B25" t="n">
-        <v>80175</v>
+        <v>80176</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129175199</v>
       </c>
       <c r="B28" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>129175673</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174795</v>
+        <v>129174832</v>
       </c>
       <c r="B32" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467160</v>
+        <v>467161</v>
       </c>
       <c r="R32" t="n">
-        <v>6859063</v>
+        <v>6859044</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,10 +4224,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174832</v>
+        <v>129174795</v>
       </c>
       <c r="B33" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467161</v>
+        <v>467160</v>
       </c>
       <c r="R33" t="n">
-        <v>6859044</v>
+        <v>6859063</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4347,7 +4347,7 @@
         <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>129175650</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5151,38 +5151,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129174718</v>
+        <v>129175136</v>
       </c>
       <c r="B41" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5190,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467122</v>
+        <v>467042</v>
       </c>
       <c r="R41" t="n">
-        <v>6859101</v>
+        <v>6858941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5244,7 +5252,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5263,46 +5270,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129175136</v>
+        <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5310,10 +5309,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467042</v>
+        <v>467122</v>
       </c>
       <c r="R42" t="n">
-        <v>6858941</v>
+        <v>6859101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5364,6 +5363,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>129174751</v>
       </c>
       <c r="B43" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>129175662</v>
       </c>
       <c r="B44" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5727,6 +5727,3139 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129196841</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79654</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>467081</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6859284</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129197427</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79625</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>467058</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6859193</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129197413</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79654</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>467002</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6859137</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129196510</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>466862</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6859147</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129197604</v>
+      </c>
+      <c r="B50" t="n">
+        <v>90152</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>467002</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6859221</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129196390</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>467022</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6859109</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129197181</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>467027</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6859149</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129196771</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78701</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>353</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>467081</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6859284</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129197410</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78701</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>353</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>467002</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6859137</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129197281</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79114</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>864</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>467009</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6859245</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129196497</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>466875</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6859133</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129196589</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79067</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>185</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>466862</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6859147</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129196354</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92819</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>467132</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6858948</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129196424</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79654</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>467042</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6859027</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129197264</v>
+      </c>
+      <c r="B60" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>466958</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6858988</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129196629</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97530</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>466840</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6858994</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129197648</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>467131</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6858952</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129196342</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92819</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>467015</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6859188</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129197170</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>467020</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6859138</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129197518</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79625</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>466892</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6859076</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129197086</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79654</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>466975</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6859149</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129197373</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78701</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>353</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>467039</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6859234</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129197561</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79625</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>466891</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6859119</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129196314</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92819</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>466991</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6859197</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129197526</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78043</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>466892</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6859076</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129196543</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79654</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>466877</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6859156</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129197157</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>466994</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6859246</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129196431</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78793</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>467059</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6859031</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175206</v>
+        <v>129175049</v>
       </c>
       <c r="B19" t="n">
-        <v>79067</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,26 +2621,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2648,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466900</v>
+        <v>466848</v>
       </c>
       <c r="R19" t="n">
-        <v>6858997</v>
+        <v>6858995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,13 +2697,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2961,10 +2966,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129175049</v>
+        <v>129175206</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>79067</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,27 +2977,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3000,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466848</v>
+        <v>466900</v>
       </c>
       <c r="R22" t="n">
-        <v>6858995</v>
+        <v>6858997</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,17 +3052,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3993,37 +3993,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129175713</v>
+        <v>129174795</v>
       </c>
       <c r="B31" t="n">
-        <v>79067</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4031,10 +4040,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467077</v>
+        <v>467160</v>
       </c>
       <c r="R31" t="n">
-        <v>6858882</v>
+        <v>6859063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,7 +4075,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4076,7 +4085,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4224,46 +4233,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174795</v>
+        <v>129175713</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>79067</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467160</v>
+        <v>467077</v>
       </c>
       <c r="R33" t="n">
-        <v>6859063</v>
+        <v>6858882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B44" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,26 +5513,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5540,10 +5541,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R44" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5575,7 +5576,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5585,7 +5586,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,7 +5600,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5613,10 +5618,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,27 +5629,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5652,10 +5656,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R45" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5687,7 +5691,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,12 +5701,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,6 +5710,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>78793</v>
+        <v>90152</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R49" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B50" t="n">
-        <v>90152</v>
+        <v>78793</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R50" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6950,36 +6950,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B57" t="n">
-        <v>79067</v>
+        <v>92819</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6988,10 +6996,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R57" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7061,44 +7069,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B58" t="n">
-        <v>92819</v>
+        <v>79067</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R58" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R59" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R60" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7744,10 +7744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197170</v>
+        <v>129197518</v>
       </c>
       <c r="B64" t="n">
-        <v>78793</v>
+        <v>79625</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467020</v>
+        <v>466892</v>
       </c>
       <c r="R64" t="n">
-        <v>6859138</v>
+        <v>6859076</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197518</v>
+        <v>129197170</v>
       </c>
       <c r="B65" t="n">
-        <v>79625</v>
+        <v>78793</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466892</v>
+        <v>467020</v>
       </c>
       <c r="R65" t="n">
-        <v>6859076</v>
+        <v>6859138</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -3188,46 +3188,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>80176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3235,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R24" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,37 +3299,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>80176</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R25" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4344,46 +4344,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>78793</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4391,10 +4382,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R34" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4417,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4427,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,37 +4455,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B35" t="n">
-        <v>78793</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R35" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,27 +5513,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5541,10 +5540,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R44" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5576,7 +5575,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5586,12 +5585,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5600,6 +5594,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5618,10 +5613,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B45" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,26 +5624,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5656,10 +5652,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R45" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5691,7 +5687,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5701,7 +5697,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5710,7 +5711,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B54" t="n">
-        <v>78701</v>
+        <v>79114</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R54" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B55" t="n">
-        <v>79114</v>
+        <v>78701</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R55" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R59" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B60" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R60" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8299,44 +8299,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B69" t="n">
-        <v>92819</v>
+        <v>78043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8345,10 +8337,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R69" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,22 +8367,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8418,36 +8410,44 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B70" t="n">
-        <v>78043</v>
+        <v>92819</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R70" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,27 +1935,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R13" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,6 +2016,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B14" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,26 +2046,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R14" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2133,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,37 +2267,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129175174</v>
+        <v>129174816</v>
       </c>
       <c r="B16" t="n">
-        <v>79067</v>
+        <v>98659</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467140</v>
+        <v>467156</v>
       </c>
       <c r="R16" t="n">
-        <v>6859092</v>
+        <v>6859054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174816</v>
+        <v>129174925</v>
       </c>
       <c r="B17" t="n">
         <v>98659</v>
@@ -2406,16 +2415,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>466878</v>
       </c>
       <c r="R17" t="n">
-        <v>6859054</v>
+        <v>6858977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,38 +2499,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129174925</v>
+        <v>129175174</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>79067</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466878</v>
+        <v>467140</v>
       </c>
       <c r="R18" t="n">
-        <v>6858977</v>
+        <v>6859092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175049</v>
+        <v>129175206</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>79067</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,27 +2621,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2649,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466848</v>
+        <v>466900</v>
       </c>
       <c r="R19" t="n">
-        <v>6858995</v>
+        <v>6858997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,17 +2696,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2726,46 +2721,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129174937</v>
+        <v>129175049</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2773,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466864</v>
+        <v>466848</v>
       </c>
       <c r="R20" t="n">
-        <v>6858963</v>
+        <v>6858995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,13 +2808,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2846,7 +2837,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174881</v>
+        <v>129174937</v>
       </c>
       <c r="B21" t="n">
         <v>98659</v>
@@ -2876,7 +2867,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2893,10 +2884,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467170</v>
+        <v>466864</v>
       </c>
       <c r="R21" t="n">
-        <v>6859051</v>
+        <v>6858963</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2966,37 +2957,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129175206</v>
+        <v>129174881</v>
       </c>
       <c r="B22" t="n">
-        <v>79067</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466900</v>
+        <v>467170</v>
       </c>
       <c r="R22" t="n">
-        <v>6858997</v>
+        <v>6859051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3993,46 +3993,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129174795</v>
+        <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>79067</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4040,10 +4031,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467160</v>
+        <v>467077</v>
       </c>
       <c r="R31" t="n">
-        <v>6859063</v>
+        <v>6858882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4075,7 +4066,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4085,7 +4076,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4113,7 +4104,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174832</v>
+        <v>129174795</v>
       </c>
       <c r="B32" t="n">
         <v>98659</v>
@@ -4143,7 +4134,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4160,10 +4151,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467161</v>
+        <v>467160</v>
       </c>
       <c r="R32" t="n">
-        <v>6859044</v>
+        <v>6859063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,37 +4224,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129175713</v>
+        <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>79067</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467077</v>
+        <v>467161</v>
       </c>
       <c r="R33" t="n">
-        <v>6858882</v>
+        <v>6859044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4344,37 +4344,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>78793</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4382,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R34" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4417,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4427,7 +4436,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,46 +4464,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>78793</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R35" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B44" t="n">
-        <v>78793</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,26 +5513,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5540,10 +5541,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R44" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5575,7 +5576,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5585,7 +5586,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,7 +5600,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5613,10 +5618,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>57723</v>
+        <v>78793</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,27 +5629,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5652,10 +5656,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R45" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5687,7 +5691,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,12 +5701,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,6 +5710,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78793</v>
+        <v>78701</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78701</v>
+        <v>78793</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R59" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R60" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7402,38 +7402,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B61" t="n">
-        <v>97530</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7441,10 +7440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R61" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7471,22 +7470,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7514,37 +7513,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>97530</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R62" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>79654</v>
+        <v>78701</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R66" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>78701</v>
+        <v>79654</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R67" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8299,36 +8299,44 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>78043</v>
+        <v>92819</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8337,10 +8345,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R69" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8367,22 +8375,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8410,44 +8418,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>92819</v>
+        <v>78043</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R70" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129139219</v>
       </c>
       <c r="B2" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129138843</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129139232</v>
       </c>
       <c r="B9" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>129175183</v>
       </c>
       <c r="B11" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>78793</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,26 +1935,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R13" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2022,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>57723</v>
+        <v>78797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,27 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R14" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2132,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>129175614</v>
       </c>
       <c r="B15" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,46 +2267,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174816</v>
+        <v>129175174</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>79071</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467140</v>
       </c>
       <c r="R16" t="n">
-        <v>6859054</v>
+        <v>6859092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174925</v>
+        <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,8 +2406,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466878</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6858977</v>
+        <v>6859054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,37 +2498,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129175174</v>
+        <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>79067</v>
+        <v>98669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467140</v>
+        <v>466878</v>
       </c>
       <c r="R18" t="n">
-        <v>6859092</v>
+        <v>6858977</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
         <v>129175206</v>
       </c>
       <c r="B19" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,38 +2721,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175049</v>
+        <v>129174937</v>
       </c>
       <c r="B20" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2760,10 +2768,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466848</v>
+        <v>466864</v>
       </c>
       <c r="R20" t="n">
-        <v>6858995</v>
+        <v>6858963</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,17 +2816,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2837,46 +2841,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174937</v>
+        <v>129175049</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2884,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466864</v>
+        <v>466848</v>
       </c>
       <c r="R21" t="n">
-        <v>6858963</v>
+        <v>6858995</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2932,13 +2928,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>129174881</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>129175691</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129175162</v>
       </c>
       <c r="B24" t="n">
-        <v>80176</v>
+        <v>80180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129175199</v>
       </c>
       <c r="B28" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>129175673</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129174795</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4344,46 +4344,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>78797</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4391,10 +4382,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R34" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4417,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4427,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,37 +4455,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B35" t="n">
-        <v>78793</v>
+        <v>98669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R35" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>129175151</v>
       </c>
       <c r="B37" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129175136</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,26 +4940,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4967,10 +4976,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>467042</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6858941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +5011,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5012,7 +5021,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,7 +5030,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5040,37 +5048,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129174718</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>98669</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5078,10 +5087,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>467122</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6859101</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5113,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5123,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5151,46 +5160,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175136</v>
+        <v>129174751</v>
       </c>
       <c r="B41" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5198,10 +5207,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467042</v>
+        <v>467131</v>
       </c>
       <c r="R41" t="n">
-        <v>6858941</v>
+        <v>6859085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5252,6 +5261,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5270,38 +5280,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174718</v>
+        <v>129175680</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5309,10 +5318,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467122</v>
+        <v>467104</v>
       </c>
       <c r="R42" t="n">
-        <v>6859101</v>
+        <v>6859032</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5344,7 +5353,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5354,7 +5363,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5382,46 +5391,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129174751</v>
+        <v>129175685</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467131</v>
+        <v>467096</v>
       </c>
       <c r="R43" t="n">
-        <v>6859085</v>
+        <v>6859018</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5505,7 +5505,7 @@
         <v>129175069</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>129196841</v>
       </c>
       <c r="B46" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>129197427</v>
       </c>
       <c r="B47" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>129197413</v>
       </c>
       <c r="B48" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>129196510</v>
       </c>
       <c r="B50" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>129196390</v>
       </c>
       <c r="B51" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78701</v>
+        <v>78797</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78793</v>
+        <v>78705</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B54" t="n">
-        <v>79114</v>
+        <v>78705</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R54" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B55" t="n">
-        <v>78701</v>
+        <v>79118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R55" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6842,7 +6842,7 @@
         <v>129196497</v>
       </c>
       <c r="B56" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>129196354</v>
       </c>
       <c r="B57" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>129196589</v>
       </c>
       <c r="B58" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>129197648</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>129197518</v>
       </c>
       <c r="B64" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>129197170</v>
       </c>
       <c r="B65" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>129197561</v>
       </c>
       <c r="B68" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129196543</v>
+        <v>129197157</v>
       </c>
       <c r="B71" t="n">
-        <v>79654</v>
+        <v>78797</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466877</v>
+        <v>466994</v>
       </c>
       <c r="R71" t="n">
-        <v>6859156</v>
+        <v>6859246</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129197157</v>
+        <v>129196543</v>
       </c>
       <c r="B72" t="n">
-        <v>78793</v>
+        <v>79658</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466994</v>
+        <v>466877</v>
       </c>
       <c r="R72" t="n">
-        <v>6859246</v>
+        <v>6859156</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8754,7 +8754,7 @@
         <v>129196431</v>
       </c>
       <c r="B73" t="n">
-        <v>78793</v>
+        <v>78797</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78797</v>
+        <v>78705</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78705</v>
+        <v>78797</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2721,46 +2721,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129174937</v>
+        <v>129175049</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2768,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466864</v>
+        <v>466848</v>
       </c>
       <c r="R20" t="n">
-        <v>6858963</v>
+        <v>6858995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2816,13 +2808,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2841,38 +2837,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129175049</v>
+        <v>129174937</v>
       </c>
       <c r="B21" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2880,10 +2884,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466848</v>
+        <v>466864</v>
       </c>
       <c r="R21" t="n">
-        <v>6858995</v>
+        <v>6858963</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,17 +2932,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2960,7 +2960,7 @@
         <v>129174881</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174848</v>
+        <v>129174912</v>
       </c>
       <c r="B26" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3447,8 +3447,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3458,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467183</v>
+        <v>467130</v>
       </c>
       <c r="R26" t="n">
-        <v>6859065</v>
+        <v>6859021</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3531,10 +3539,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129174912</v>
+        <v>129174848</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3559,16 +3567,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467130</v>
+        <v>467183</v>
       </c>
       <c r="R27" t="n">
-        <v>6859021</v>
+        <v>6859065</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129174795</v>
       </c>
       <c r="B32" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4344,37 +4344,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>78797</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4382,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R34" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4417,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4427,7 +4436,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,46 +4464,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B35" t="n">
-        <v>98669</v>
+        <v>78797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R35" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175136</v>
+        <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,35 +4940,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4976,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467042</v>
+        <v>467104</v>
       </c>
       <c r="R39" t="n">
-        <v>6858941</v>
+        <v>6859032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5011,7 +5002,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5021,7 +5012,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,6 +5021,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5048,38 +5040,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129174718</v>
+        <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5087,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467122</v>
+        <v>467096</v>
       </c>
       <c r="R40" t="n">
-        <v>6859101</v>
+        <v>6859018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5113,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5123,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5160,46 +5151,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129174751</v>
+        <v>129175136</v>
       </c>
       <c r="B41" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5207,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467131</v>
+        <v>467042</v>
       </c>
       <c r="R41" t="n">
-        <v>6859085</v>
+        <v>6858941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5261,7 +5252,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5280,37 +5270,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129175680</v>
+        <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5318,10 +5309,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467104</v>
+        <v>467122</v>
       </c>
       <c r="R42" t="n">
-        <v>6859032</v>
+        <v>6859101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5353,7 +5344,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5363,7 +5354,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5391,37 +5382,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175685</v>
+        <v>129174751</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>98676</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467096</v>
+        <v>467131</v>
       </c>
       <c r="R43" t="n">
-        <v>6859018</v>
+        <v>6859085</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B49" t="n">
-        <v>90156</v>
+        <v>78797</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R49" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B50" t="n">
-        <v>78797</v>
+        <v>90163</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R50" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6950,44 +6950,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B57" t="n">
-        <v>92826</v>
+        <v>79071</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6996,10 +6988,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R57" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7069,36 +7061,44 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>79071</v>
+        <v>92833</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R58" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7516,7 +7516,7 @@
         <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B66" t="n">
-        <v>78705</v>
+        <v>79658</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R66" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B67" t="n">
-        <v>79658</v>
+        <v>78705</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R67" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8302,7 +8302,7 @@
         <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197157</v>
+        <v>129196543</v>
       </c>
       <c r="B71" t="n">
-        <v>78797</v>
+        <v>79658</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466994</v>
+        <v>466877</v>
       </c>
       <c r="R71" t="n">
-        <v>6859246</v>
+        <v>6859156</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129196543</v>
+        <v>129197157</v>
       </c>
       <c r="B72" t="n">
-        <v>79658</v>
+        <v>78797</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466877</v>
+        <v>466994</v>
       </c>
       <c r="R72" t="n">
-        <v>6859156</v>
+        <v>6859246</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129139219</v>
       </c>
       <c r="B2" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129138843</v>
       </c>
       <c r="B3" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129139232</v>
       </c>
       <c r="B9" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>129175183</v>
       </c>
       <c r="B11" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>129175614</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,37 +2267,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129175174</v>
+        <v>129174816</v>
       </c>
       <c r="B16" t="n">
-        <v>79071</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467140</v>
+        <v>467156</v>
       </c>
       <c r="R16" t="n">
-        <v>6859092</v>
+        <v>6859054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174816</v>
+        <v>129174925</v>
       </c>
       <c r="B17" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,16 +2415,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>466878</v>
       </c>
       <c r="R17" t="n">
-        <v>6859054</v>
+        <v>6858977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,38 +2499,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129174925</v>
+        <v>129175174</v>
       </c>
       <c r="B18" t="n">
-        <v>98676</v>
+        <v>79073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466878</v>
+        <v>467140</v>
       </c>
       <c r="R18" t="n">
-        <v>6858977</v>
+        <v>6859092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
         <v>129175206</v>
       </c>
       <c r="B19" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>129175049</v>
       </c>
       <c r="B20" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
         <v>129174937</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>129174881</v>
       </c>
       <c r="B22" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>129175691</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3188,37 +3188,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B24" t="n">
-        <v>80180</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3226,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R24" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3299,46 +3308,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B25" t="n">
-        <v>98676</v>
+        <v>80182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R25" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174912</v>
+        <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3447,16 +3447,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3466,10 +3458,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467130</v>
+        <v>467183</v>
       </c>
       <c r="R26" t="n">
-        <v>6859021</v>
+        <v>6859065</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,10 +3531,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129174848</v>
+        <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,8 +3559,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467183</v>
+        <v>467130</v>
       </c>
       <c r="R27" t="n">
-        <v>6859065</v>
+        <v>6859021</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3654,7 +3654,7 @@
         <v>129175199</v>
       </c>
       <c r="B28" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>129175673</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129174795</v>
       </c>
       <c r="B32" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4344,46 +4344,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>78799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4391,10 +4382,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R34" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4417,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4427,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,37 +4455,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B35" t="n">
-        <v>78797</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R35" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>129175151</v>
       </c>
       <c r="B37" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>129175136</v>
       </c>
       <c r="B41" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>129174751</v>
       </c>
       <c r="B43" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>129175069</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5621,7 +5621,7 @@
         <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>129196841</v>
       </c>
       <c r="B46" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>129197427</v>
       </c>
       <c r="B47" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>129197413</v>
       </c>
       <c r="B48" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>129196510</v>
       </c>
       <c r="B49" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>129197604</v>
       </c>
       <c r="B50" t="n">
-        <v>90163</v>
+        <v>90165</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>129196390</v>
       </c>
       <c r="B51" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78705</v>
+        <v>78799</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78797</v>
+        <v>78707</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B54" t="n">
-        <v>78705</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R54" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B55" t="n">
-        <v>79118</v>
+        <v>78707</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R55" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6842,7 +6842,7 @@
         <v>129196497</v>
       </c>
       <c r="B56" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6950,36 +6950,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B57" t="n">
-        <v>79071</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6988,10 +6996,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R57" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7061,44 +7069,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B58" t="n">
-        <v>92833</v>
+        <v>79073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R58" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R59" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B60" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R60" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7402,37 +7402,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>97549</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7440,10 +7441,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R61" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,22 +7471,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7513,38 +7514,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B62" t="n">
-        <v>97547</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R62" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>129197518</v>
       </c>
       <c r="B64" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>129197170</v>
       </c>
       <c r="B65" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>79658</v>
+        <v>78707</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R66" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>78705</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R67" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8191,7 +8191,7 @@
         <v>129197561</v>
       </c>
       <c r="B68" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>78047</v>
+        <v>78049</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>129196543</v>
       </c>
       <c r="B71" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>129197157</v>
       </c>
       <c r="B72" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>129196431</v>
       </c>
       <c r="B73" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>78799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,27 +1935,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R13" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,6 +2016,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B14" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,26 +2046,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R14" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2133,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,46 +2267,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174816</v>
+        <v>129175174</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467140</v>
       </c>
       <c r="R16" t="n">
-        <v>6859054</v>
+        <v>6859092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174925</v>
+        <v>129174816</v>
       </c>
       <c r="B17" t="n">
         <v>98678</v>
@@ -2415,8 +2406,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466878</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6858977</v>
+        <v>6859054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,37 +2498,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129175174</v>
+        <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467140</v>
+        <v>466878</v>
       </c>
       <c r="R18" t="n">
-        <v>6859092</v>
+        <v>6858977</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,37 +2610,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175206</v>
+        <v>129174937</v>
       </c>
       <c r="B19" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2648,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466900</v>
+        <v>466864</v>
       </c>
       <c r="R19" t="n">
-        <v>6858997</v>
+        <v>6858963</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,38 +2730,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175049</v>
+        <v>129174881</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2760,10 +2777,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466848</v>
+        <v>467170</v>
       </c>
       <c r="R20" t="n">
-        <v>6858995</v>
+        <v>6859051</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,17 +2825,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2837,46 +2850,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174937</v>
+        <v>129175206</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2884,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466864</v>
+        <v>466900</v>
       </c>
       <c r="R21" t="n">
-        <v>6858963</v>
+        <v>6858997</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,46 +2961,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174881</v>
+        <v>129175049</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +3000,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467170</v>
+        <v>466848</v>
       </c>
       <c r="R22" t="n">
-        <v>6859051</v>
+        <v>6858995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,13 +3048,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3188,46 +3188,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>80182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3235,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R24" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,37 +3299,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>80182</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R25" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3993,37 +3993,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129175713</v>
+        <v>129174795</v>
       </c>
       <c r="B31" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4031,10 +4040,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467077</v>
+        <v>467160</v>
       </c>
       <c r="R31" t="n">
-        <v>6858882</v>
+        <v>6859063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,7 +4075,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4076,7 +4085,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4104,7 +4113,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174795</v>
+        <v>129174832</v>
       </c>
       <c r="B32" t="n">
         <v>98678</v>
@@ -4134,7 +4143,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4151,10 +4160,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467160</v>
+        <v>467161</v>
       </c>
       <c r="R32" t="n">
-        <v>6859063</v>
+        <v>6859044</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,46 +4233,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174832</v>
+        <v>129175713</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467161</v>
+        <v>467077</v>
       </c>
       <c r="R33" t="n">
-        <v>6859044</v>
+        <v>6858882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>78799</v>
+        <v>90165</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R49" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B50" t="n">
-        <v>90165</v>
+        <v>78799</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R50" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>78707</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R54" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B55" t="n">
-        <v>78707</v>
+        <v>79120</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R55" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6950,44 +6950,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>79073</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6996,10 +6988,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R57" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7069,36 +7061,44 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>79073</v>
+        <v>92835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R58" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R59" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R60" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7402,38 +7402,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B61" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7441,10 +7440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R61" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7471,22 +7470,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7514,37 +7513,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>97549</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R62" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B66" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R66" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R67" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8299,44 +8299,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B69" t="n">
-        <v>92835</v>
+        <v>78049</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8345,10 +8337,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R69" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,22 +8367,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8418,36 +8410,44 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B70" t="n">
-        <v>78049</v>
+        <v>92835</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R70" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -2610,46 +2610,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129174937</v>
+        <v>129175206</v>
       </c>
       <c r="B19" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2657,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466864</v>
+        <v>466900</v>
       </c>
       <c r="R19" t="n">
-        <v>6858963</v>
+        <v>6858997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,7 +2721,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129174881</v>
+        <v>129174937</v>
       </c>
       <c r="B20" t="n">
         <v>98678</v>
@@ -2760,7 +2751,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2777,10 +2768,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467170</v>
+        <v>466864</v>
       </c>
       <c r="R20" t="n">
-        <v>6859051</v>
+        <v>6858963</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,37 +2841,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129175206</v>
+        <v>129174881</v>
       </c>
       <c r="B21" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466900</v>
+        <v>467170</v>
       </c>
       <c r="R21" t="n">
-        <v>6858997</v>
+        <v>6859051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3993,46 +3993,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129174795</v>
+        <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4040,10 +4031,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467160</v>
+        <v>467077</v>
       </c>
       <c r="R31" t="n">
-        <v>6859063</v>
+        <v>6858882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4075,7 +4066,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4085,7 +4076,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4113,7 +4104,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174832</v>
+        <v>129174795</v>
       </c>
       <c r="B32" t="n">
         <v>98678</v>
@@ -4143,7 +4134,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4160,10 +4151,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467161</v>
+        <v>467160</v>
       </c>
       <c r="R32" t="n">
-        <v>6859044</v>
+        <v>6859063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,37 +4224,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129175713</v>
+        <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>79073</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467077</v>
+        <v>467161</v>
       </c>
       <c r="R33" t="n">
-        <v>6858882</v>
+        <v>6859044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4344,37 +4344,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>98678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4382,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R34" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4417,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4427,7 +4436,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,46 +4464,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>78799</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R35" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -7402,37 +7402,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>97549</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7440,10 +7441,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R61" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,22 +7471,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7513,38 +7514,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B62" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R62" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,44 +1231,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139492</v>
+        <v>129139418</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>97581</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1278,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467077</v>
+        <v>467036</v>
       </c>
       <c r="R7" t="n">
-        <v>6858863</v>
+        <v>6858929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,36 +1343,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129139418</v>
+        <v>129139492</v>
       </c>
       <c r="B8" t="n">
-        <v>97555</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467036</v>
+        <v>467077</v>
       </c>
       <c r="R8" t="n">
-        <v>6858929</v>
+        <v>6858863</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,26 +1935,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R13" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2022,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>78799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,27 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R14" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2132,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175206</v>
+        <v>129175049</v>
       </c>
       <c r="B19" t="n">
-        <v>79073</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,26 +2621,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2648,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466900</v>
+        <v>466848</v>
       </c>
       <c r="R19" t="n">
-        <v>6858997</v>
+        <v>6858995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,13 +2697,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2721,46 +2726,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129174937</v>
+        <v>129175206</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2768,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466864</v>
+        <v>466900</v>
       </c>
       <c r="R20" t="n">
-        <v>6858963</v>
+        <v>6858997</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174881</v>
+        <v>129174937</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,7 +2867,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2888,10 +2884,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467170</v>
+        <v>466864</v>
       </c>
       <c r="R21" t="n">
-        <v>6859051</v>
+        <v>6858963</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,38 +2957,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129175049</v>
+        <v>129174881</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3000,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466848</v>
+        <v>467170</v>
       </c>
       <c r="R22" t="n">
-        <v>6858995</v>
+        <v>6859051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,17 +3052,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3188,37 +3188,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B24" t="n">
-        <v>80182</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3226,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R24" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3299,46 +3308,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B25" t="n">
-        <v>98678</v>
+        <v>80182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R25" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174848</v>
+        <v>129174912</v>
       </c>
       <c r="B26" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3447,8 +3447,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3458,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467183</v>
+        <v>467130</v>
       </c>
       <c r="R26" t="n">
-        <v>6859065</v>
+        <v>6859021</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3531,10 +3539,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129174912</v>
+        <v>129174848</v>
       </c>
       <c r="B27" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3559,16 +3567,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467130</v>
+        <v>467183</v>
       </c>
       <c r="R27" t="n">
-        <v>6859021</v>
+        <v>6859065</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3993,37 +3993,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129175713</v>
+        <v>129174832</v>
       </c>
       <c r="B31" t="n">
-        <v>79073</v>
+        <v>98704</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4031,10 +4040,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467077</v>
+        <v>467161</v>
       </c>
       <c r="R31" t="n">
-        <v>6858882</v>
+        <v>6859044</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,7 +4075,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4076,7 +4085,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4104,46 +4113,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174795</v>
+        <v>129175713</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>79073</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467160</v>
+        <v>467077</v>
       </c>
       <c r="R32" t="n">
-        <v>6859063</v>
+        <v>6858882</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4224,10 +4224,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174832</v>
+        <v>129174795</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467161</v>
+        <v>467160</v>
       </c>
       <c r="R33" t="n">
-        <v>6859044</v>
+        <v>6859063</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4344,46 +4344,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B34" t="n">
-        <v>98678</v>
+        <v>78799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4391,10 +4382,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R34" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4417,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4427,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,37 +4455,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B35" t="n">
-        <v>78799</v>
+        <v>98704</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R35" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,37 +4929,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129174718</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4967,10 +4968,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>467122</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6859101</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +5003,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5012,7 +5013,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5040,37 +5041,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129174751</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>98704</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5078,10 +5088,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>467131</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6859085</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5113,7 +5123,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5123,7 +5133,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5151,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175136</v>
+        <v>129175680</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5162,35 +5172,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5198,10 +5199,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467042</v>
+        <v>467104</v>
       </c>
       <c r="R41" t="n">
-        <v>6858941</v>
+        <v>6859032</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5233,7 +5234,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5243,7 +5244,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5252,6 +5253,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5270,38 +5272,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174718</v>
+        <v>129175685</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5309,10 +5310,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467122</v>
+        <v>467096</v>
       </c>
       <c r="R42" t="n">
-        <v>6859101</v>
+        <v>6859018</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5344,7 +5345,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5354,7 +5355,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5382,46 +5383,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129174751</v>
+        <v>129175136</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5429,10 +5430,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467131</v>
+        <v>467042</v>
       </c>
       <c r="R43" t="n">
-        <v>6859085</v>
+        <v>6858941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5483,7 +5484,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>78799</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,27 +5513,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5541,10 +5540,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R44" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5576,7 +5575,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5586,12 +5585,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5600,6 +5594,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5618,10 +5613,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B45" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,26 +5624,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5656,10 +5652,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R45" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5691,7 +5687,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5701,7 +5697,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5710,7 +5711,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>90165</v>
+        <v>90166</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7064,7 +7064,7 @@
         <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R59" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B60" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R60" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7405,7 +7405,7 @@
         <v>129196629</v>
       </c>
       <c r="B61" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8299,36 +8299,44 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>78049</v>
+        <v>92821</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8337,10 +8345,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R69" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8367,22 +8375,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8410,44 +8418,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>92835</v>
+        <v>78049</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R70" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139418</v>
       </c>
       <c r="B7" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>129139492</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>78799</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,27 +1935,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R13" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,6 +2016,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B14" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,26 +2046,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R14" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2133,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,37 +2267,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129175174</v>
+        <v>129174816</v>
       </c>
       <c r="B16" t="n">
-        <v>79073</v>
+        <v>98705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467140</v>
+        <v>467156</v>
       </c>
       <c r="R16" t="n">
-        <v>6859092</v>
+        <v>6859054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174816</v>
+        <v>129174925</v>
       </c>
       <c r="B17" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,16 +2415,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>466878</v>
       </c>
       <c r="R17" t="n">
-        <v>6859054</v>
+        <v>6858977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,38 +2499,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129174925</v>
+        <v>129175174</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>79073</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466878</v>
+        <v>467140</v>
       </c>
       <c r="R18" t="n">
-        <v>6858977</v>
+        <v>6859092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2840,7 +2840,7 @@
         <v>129174937</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>129174881</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3188,46 +3188,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>80182</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3235,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R24" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,37 +3299,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>80182</v>
+        <v>98705</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R25" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174912</v>
+        <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3447,16 +3447,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3466,10 +3458,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467130</v>
+        <v>467183</v>
       </c>
       <c r="R26" t="n">
-        <v>6859021</v>
+        <v>6859065</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,10 +3531,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129174848</v>
+        <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,8 +3559,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467183</v>
+        <v>467130</v>
       </c>
       <c r="R27" t="n">
-        <v>6859065</v>
+        <v>6859021</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3993,46 +3993,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129174832</v>
+        <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>98704</v>
+        <v>79073</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4040,10 +4031,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467161</v>
+        <v>467077</v>
       </c>
       <c r="R31" t="n">
-        <v>6859044</v>
+        <v>6858882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4075,7 +4066,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4085,7 +4076,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4113,37 +4104,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129175713</v>
+        <v>129174795</v>
       </c>
       <c r="B32" t="n">
-        <v>79073</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467077</v>
+        <v>467160</v>
       </c>
       <c r="R32" t="n">
-        <v>6858882</v>
+        <v>6859063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4224,10 +4224,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174795</v>
+        <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467160</v>
+        <v>467161</v>
       </c>
       <c r="R33" t="n">
-        <v>6859063</v>
+        <v>6859044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4344,37 +4344,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>98705</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4382,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R34" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4417,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4427,7 +4436,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,46 +4464,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B35" t="n">
-        <v>98704</v>
+        <v>78799</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R35" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,38 +4929,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129174718</v>
+        <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4968,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467122</v>
+        <v>467104</v>
       </c>
       <c r="R39" t="n">
-        <v>6859101</v>
+        <v>6859032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5003,7 +5002,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5013,7 +5012,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5041,46 +5040,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129174751</v>
+        <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>98704</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5088,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467131</v>
+        <v>467096</v>
       </c>
       <c r="R40" t="n">
-        <v>6859085</v>
+        <v>6859018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5123,7 +5113,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5133,7 +5123,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,37 +5151,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175680</v>
+        <v>129174718</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5199,10 +5190,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467104</v>
+        <v>467122</v>
       </c>
       <c r="R41" t="n">
-        <v>6859032</v>
+        <v>6859101</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5234,7 +5225,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5244,7 +5235,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5272,37 +5263,46 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129175685</v>
+        <v>129174751</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>98705</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467096</v>
+        <v>467131</v>
       </c>
       <c r="R42" t="n">
-        <v>6859018</v>
+        <v>6859085</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B44" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,26 +5513,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5540,10 +5541,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R44" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5575,7 +5576,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5585,7 +5586,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,7 +5600,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5613,10 +5618,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>78799</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,27 +5629,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5652,10 +5656,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R45" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5687,7 +5691,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,12 +5701,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,6 +5710,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B49" t="n">
-        <v>90166</v>
+        <v>78799</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R49" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B50" t="n">
-        <v>78799</v>
+        <v>90166</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R50" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B54" t="n">
-        <v>78707</v>
+        <v>79120</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R54" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B55" t="n">
-        <v>79120</v>
+        <v>78707</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R55" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6950,36 +6950,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B57" t="n">
-        <v>79073</v>
+        <v>92822</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6988,10 +6996,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R57" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7061,44 +7069,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B58" t="n">
-        <v>92821</v>
+        <v>79073</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R58" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7402,38 +7402,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B61" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7441,10 +7440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R61" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7471,22 +7470,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7514,37 +7513,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>97576</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R62" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197518</v>
+        <v>129197170</v>
       </c>
       <c r="B64" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466892</v>
+        <v>467020</v>
       </c>
       <c r="R64" t="n">
-        <v>6859076</v>
+        <v>6859138</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197170</v>
+        <v>129197518</v>
       </c>
       <c r="B65" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467020</v>
+        <v>466892</v>
       </c>
       <c r="R65" t="n">
-        <v>6859138</v>
+        <v>6859076</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8302,7 +8302,7 @@
         <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,36 +1231,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139418</v>
+        <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>97582</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1270,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467036</v>
+        <v>467077</v>
       </c>
       <c r="R7" t="n">
-        <v>6858929</v>
+        <v>6858863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,44 +1351,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129139492</v>
+        <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>97583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467077</v>
+        <v>467036</v>
       </c>
       <c r="R8" t="n">
-        <v>6858863</v>
+        <v>6858929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>78799</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,26 +1935,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R13" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2022,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>78799</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,27 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R14" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2132,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,46 +2267,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174816</v>
+        <v>129175174</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>79073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467140</v>
       </c>
       <c r="R16" t="n">
-        <v>6859054</v>
+        <v>6859092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174925</v>
+        <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,8 +2406,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466878</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6858977</v>
+        <v>6859054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,37 +2498,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129175174</v>
+        <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>79073</v>
+        <v>98706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467140</v>
+        <v>466878</v>
       </c>
       <c r="R18" t="n">
-        <v>6859092</v>
+        <v>6858977</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2726,37 +2726,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175206</v>
+        <v>129174937</v>
       </c>
       <c r="B20" t="n">
-        <v>79073</v>
+        <v>98706</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2764,10 +2773,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466900</v>
+        <v>466864</v>
       </c>
       <c r="R20" t="n">
-        <v>6858997</v>
+        <v>6858963</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2837,10 +2846,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174937</v>
+        <v>129174881</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,7 +2876,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2884,10 +2893,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466864</v>
+        <v>467170</v>
       </c>
       <c r="R21" t="n">
-        <v>6858963</v>
+        <v>6859051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,46 +2966,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174881</v>
+        <v>129175206</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>79073</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467170</v>
+        <v>466900</v>
       </c>
       <c r="R22" t="n">
-        <v>6859051</v>
+        <v>6858997</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3188,37 +3188,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B24" t="n">
-        <v>80182</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3226,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R24" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3299,46 +3308,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B25" t="n">
-        <v>98705</v>
+        <v>80182</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R25" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3422,7 +3422,7 @@
         <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129174795</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4344,46 +4344,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B34" t="n">
-        <v>98705</v>
+        <v>78799</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4391,10 +4382,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R34" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4417,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4427,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,37 +4455,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B35" t="n">
-        <v>78799</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R35" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4929,37 +4929,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129174718</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4967,10 +4968,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>467122</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6859101</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +5003,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5012,7 +5013,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5040,37 +5041,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129174751</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>98706</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5078,10 +5088,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>467131</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6859085</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5113,7 +5123,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5123,7 +5133,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5151,38 +5161,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129174718</v>
+        <v>129175680</v>
       </c>
       <c r="B41" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5190,10 +5199,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467122</v>
+        <v>467104</v>
       </c>
       <c r="R41" t="n">
-        <v>6859101</v>
+        <v>6859032</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5225,7 +5234,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5235,7 +5244,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5263,46 +5272,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174751</v>
+        <v>129175685</v>
       </c>
       <c r="B42" t="n">
-        <v>98705</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467131</v>
+        <v>467096</v>
       </c>
       <c r="R42" t="n">
-        <v>6859085</v>
+        <v>6859018</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>78799</v>
+        <v>90166</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R49" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B50" t="n">
-        <v>90166</v>
+        <v>78799</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R50" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78707</v>
+        <v>78799</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78799</v>
+        <v>78707</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R59" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R60" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7516,7 +7516,7 @@
         <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>97576</v>
+        <v>97577</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197170</v>
+        <v>129197518</v>
       </c>
       <c r="B64" t="n">
-        <v>78799</v>
+        <v>79631</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467020</v>
+        <v>466892</v>
       </c>
       <c r="R64" t="n">
-        <v>6859138</v>
+        <v>6859076</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197518</v>
+        <v>129197170</v>
       </c>
       <c r="B65" t="n">
-        <v>79631</v>
+        <v>78799</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466892</v>
+        <v>467020</v>
       </c>
       <c r="R65" t="n">
-        <v>6859076</v>
+        <v>6859138</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>79660</v>
+        <v>78707</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R66" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>78707</v>
+        <v>79660</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R67" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8529,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129196543</v>
+        <v>129197157</v>
       </c>
       <c r="B71" t="n">
-        <v>79660</v>
+        <v>78799</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466877</v>
+        <v>466994</v>
       </c>
       <c r="R71" t="n">
-        <v>6859156</v>
+        <v>6859246</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129197157</v>
+        <v>129196543</v>
       </c>
       <c r="B72" t="n">
-        <v>78799</v>
+        <v>79660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466994</v>
+        <v>466877</v>
       </c>
       <c r="R72" t="n">
-        <v>6859246</v>
+        <v>6859156</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129139219</v>
       </c>
       <c r="B2" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129138843</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129139232</v>
       </c>
       <c r="B9" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>129175183</v>
       </c>
       <c r="B11" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2267,37 +2267,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129175174</v>
+        <v>129174816</v>
       </c>
       <c r="B16" t="n">
-        <v>79073</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467140</v>
+        <v>467156</v>
       </c>
       <c r="R16" t="n">
-        <v>6859092</v>
+        <v>6859054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2387,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174816</v>
+        <v>129174925</v>
       </c>
       <c r="B17" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2406,16 +2415,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>466878</v>
       </c>
       <c r="R17" t="n">
-        <v>6859054</v>
+        <v>6858977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,38 +2499,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129174925</v>
+        <v>129175174</v>
       </c>
       <c r="B18" t="n">
-        <v>98706</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466878</v>
+        <v>467140</v>
       </c>
       <c r="R18" t="n">
-        <v>6858977</v>
+        <v>6859092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175049</v>
+        <v>129175206</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,27 +2621,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2649,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466848</v>
+        <v>466900</v>
       </c>
       <c r="R19" t="n">
-        <v>6858995</v>
+        <v>6858997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,17 +2696,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2729,7 +2724,7 @@
         <v>129174937</v>
       </c>
       <c r="B20" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2849,7 +2844,7 @@
         <v>129174881</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2966,10 +2961,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129175206</v>
+        <v>129175049</v>
       </c>
       <c r="B22" t="n">
-        <v>79073</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2977,26 +2972,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +3000,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466900</v>
+        <v>466848</v>
       </c>
       <c r="R22" t="n">
-        <v>6858997</v>
+        <v>6858995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,13 +3048,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>129175691</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129174865</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>129175162</v>
       </c>
       <c r="B25" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174848</v>
+        <v>129174912</v>
       </c>
       <c r="B26" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3447,8 +3447,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3458,10 +3466,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467183</v>
+        <v>467130</v>
       </c>
       <c r="R26" t="n">
-        <v>6859065</v>
+        <v>6859021</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3531,10 +3539,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129174912</v>
+        <v>129174848</v>
       </c>
       <c r="B27" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3559,16 +3567,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467130</v>
+        <v>467183</v>
       </c>
       <c r="R27" t="n">
-        <v>6859021</v>
+        <v>6859065</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3654,7 +3654,7 @@
         <v>129175199</v>
       </c>
       <c r="B28" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>129175673</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3993,37 +3993,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129175713</v>
+        <v>129174795</v>
       </c>
       <c r="B31" t="n">
-        <v>79073</v>
+        <v>98710</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4031,10 +4040,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467077</v>
+        <v>467160</v>
       </c>
       <c r="R31" t="n">
-        <v>6858882</v>
+        <v>6859063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,7 +4075,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4076,7 +4085,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4104,10 +4113,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174795</v>
+        <v>129174832</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,7 +4143,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4151,10 +4160,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467160</v>
+        <v>467161</v>
       </c>
       <c r="R32" t="n">
-        <v>6859063</v>
+        <v>6859044</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,46 +4233,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174832</v>
+        <v>129175713</v>
       </c>
       <c r="B33" t="n">
-        <v>98706</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467161</v>
+        <v>467077</v>
       </c>
       <c r="R33" t="n">
-        <v>6859044</v>
+        <v>6858882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4347,7 +4347,7 @@
         <v>129175650</v>
       </c>
       <c r="B34" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>129174783</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,38 +4929,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129174718</v>
+        <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4968,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467122</v>
+        <v>467104</v>
       </c>
       <c r="R39" t="n">
-        <v>6859101</v>
+        <v>6859032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5003,7 +5002,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5013,7 +5012,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5041,46 +5040,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129174751</v>
+        <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>98706</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5088,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467131</v>
+        <v>467096</v>
       </c>
       <c r="R40" t="n">
-        <v>6859085</v>
+        <v>6859018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5123,7 +5113,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5133,7 +5123,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,37 +5151,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175680</v>
+        <v>129174751</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5199,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467104</v>
+        <v>467131</v>
       </c>
       <c r="R41" t="n">
-        <v>6859032</v>
+        <v>6859085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5234,7 +5233,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5244,7 +5243,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5272,37 +5271,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129175685</v>
+        <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>98710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467096</v>
+        <v>467122</v>
       </c>
       <c r="R42" t="n">
-        <v>6859018</v>
+        <v>6859101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5621,7 +5621,7 @@
         <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>129196841</v>
       </c>
       <c r="B46" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>129197427</v>
       </c>
       <c r="B47" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>129197413</v>
       </c>
       <c r="B48" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B49" t="n">
-        <v>90166</v>
+        <v>78801</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R49" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B50" t="n">
-        <v>78799</v>
+        <v>90169</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R50" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6287,7 +6287,7 @@
         <v>129196390</v>
       </c>
       <c r="B51" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78799</v>
+        <v>78709</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78707</v>
+        <v>78801</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B54" t="n">
-        <v>79120</v>
+        <v>78709</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R54" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B55" t="n">
-        <v>78707</v>
+        <v>79122</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R55" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6842,7 +6842,7 @@
         <v>129196497</v>
       </c>
       <c r="B56" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6950,44 +6950,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B57" t="n">
-        <v>92822</v>
+        <v>79075</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6996,10 +6988,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R57" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7069,36 +7061,44 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>79073</v>
+        <v>92825</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R58" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R59" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B60" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R60" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7405,7 +7405,7 @@
         <v>129197648</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197518</v>
+        <v>129197170</v>
       </c>
       <c r="B64" t="n">
-        <v>79631</v>
+        <v>78801</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466892</v>
+        <v>467020</v>
       </c>
       <c r="R64" t="n">
-        <v>6859076</v>
+        <v>6859138</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197170</v>
+        <v>129197518</v>
       </c>
       <c r="B65" t="n">
-        <v>78799</v>
+        <v>79633</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467020</v>
+        <v>466892</v>
       </c>
       <c r="R65" t="n">
-        <v>6859138</v>
+        <v>6859076</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7969,7 +7969,7 @@
         <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>78707</v>
+        <v>78709</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>129197561</v>
       </c>
       <c r="B68" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>78049</v>
+        <v>78051</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197157</v>
+        <v>129196543</v>
       </c>
       <c r="B71" t="n">
-        <v>78799</v>
+        <v>79662</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466994</v>
+        <v>466877</v>
       </c>
       <c r="R71" t="n">
-        <v>6859246</v>
+        <v>6859156</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129196543</v>
+        <v>129197157</v>
       </c>
       <c r="B72" t="n">
-        <v>79660</v>
+        <v>78801</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466877</v>
+        <v>466994</v>
       </c>
       <c r="R72" t="n">
-        <v>6859156</v>
+        <v>6859246</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8754,7 +8754,7 @@
         <v>129196431</v>
       </c>
       <c r="B73" t="n">
-        <v>78799</v>
+        <v>78801</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -3188,46 +3188,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>80184</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3235,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R24" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,37 +3299,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>80184</v>
+        <v>98710</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R25" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -5151,46 +5151,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129174751</v>
+        <v>129175136</v>
       </c>
       <c r="B41" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467131</v>
+        <v>467042</v>
       </c>
       <c r="R41" t="n">
-        <v>6859085</v>
+        <v>6858941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5252,7 +5252,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5271,7 +5270,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174718</v>
+        <v>129174751</v>
       </c>
       <c r="B42" t="n">
         <v>98710</v>
@@ -5299,8 +5298,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5310,10 +5317,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467122</v>
+        <v>467131</v>
       </c>
       <c r="R42" t="n">
-        <v>6859101</v>
+        <v>6859085</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5383,46 +5390,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175136</v>
+        <v>129174718</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5430,10 +5429,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467042</v>
+        <v>467122</v>
       </c>
       <c r="R43" t="n">
-        <v>6858941</v>
+        <v>6859101</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5484,6 +5483,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129139219</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129138843</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129139232</v>
       </c>
       <c r="B9" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>129175183</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129174816</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129174925</v>
       </c>
       <c r="B17" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>129175174</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,37 +2610,46 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175206</v>
+        <v>129174937</v>
       </c>
       <c r="B19" t="n">
-        <v>79075</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2648,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466900</v>
+        <v>466864</v>
       </c>
       <c r="R19" t="n">
-        <v>6858997</v>
+        <v>6858963</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2721,10 +2730,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129174937</v>
+        <v>129174881</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,7 +2760,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2768,10 +2777,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466864</v>
+        <v>467170</v>
       </c>
       <c r="R20" t="n">
-        <v>6858963</v>
+        <v>6859051</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,46 +2850,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174881</v>
+        <v>129175206</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467170</v>
+        <v>466900</v>
       </c>
       <c r="R21" t="n">
-        <v>6859051</v>
+        <v>6858997</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3080,7 +3080,7 @@
         <v>129175691</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129175162</v>
       </c>
       <c r="B24" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3419,10 +3419,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174912</v>
+        <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3447,16 +3447,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3466,10 +3458,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467130</v>
+        <v>467183</v>
       </c>
       <c r="R26" t="n">
-        <v>6859021</v>
+        <v>6859065</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3539,10 +3531,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129174848</v>
+        <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3567,8 +3559,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>467183</v>
+        <v>467130</v>
       </c>
       <c r="R27" t="n">
-        <v>6859065</v>
+        <v>6859021</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3654,7 +3654,7 @@
         <v>129175199</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>129175673</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129174795</v>
       </c>
       <c r="B31" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>129174832</v>
       </c>
       <c r="B32" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>129175713</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4344,37 +4344,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>78801</v>
+        <v>98712</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4382,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R34" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4417,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4427,7 +4436,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,46 +4464,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B35" t="n">
-        <v>98710</v>
+        <v>78802</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R35" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174751</v>
+        <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5298,16 +5298,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5317,10 +5309,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467131</v>
+        <v>467122</v>
       </c>
       <c r="R42" t="n">
-        <v>6859085</v>
+        <v>6859101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5390,10 +5382,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129174718</v>
+        <v>129174751</v>
       </c>
       <c r="B43" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5418,8 +5410,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467122</v>
+        <v>467131</v>
       </c>
       <c r="R43" t="n">
-        <v>6859101</v>
+        <v>6859085</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5621,7 +5621,7 @@
         <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>129196841</v>
       </c>
       <c r="B46" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>129197427</v>
       </c>
       <c r="B47" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>129197413</v>
       </c>
       <c r="B48" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>78801</v>
+        <v>90171</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R49" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B50" t="n">
-        <v>90169</v>
+        <v>78802</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R50" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6287,7 +6287,7 @@
         <v>129196390</v>
       </c>
       <c r="B51" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>129197410</v>
       </c>
       <c r="B54" t="n">
-        <v>78709</v>
+        <v>78710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>129197281</v>
       </c>
       <c r="B55" t="n">
-        <v>79122</v>
+        <v>79123</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>129196497</v>
       </c>
       <c r="B56" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>129196589</v>
       </c>
       <c r="B57" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7064,7 +7064,7 @@
         <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R59" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R60" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7402,37 +7402,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>97583</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7440,10 +7441,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R61" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,22 +7471,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7513,38 +7514,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B62" t="n">
-        <v>97581</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R62" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197170</v>
+        <v>129197518</v>
       </c>
       <c r="B64" t="n">
-        <v>78801</v>
+        <v>79634</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467020</v>
+        <v>466892</v>
       </c>
       <c r="R64" t="n">
-        <v>6859138</v>
+        <v>6859076</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197518</v>
+        <v>129197170</v>
       </c>
       <c r="B65" t="n">
-        <v>79633</v>
+        <v>78802</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466892</v>
+        <v>467020</v>
       </c>
       <c r="R65" t="n">
-        <v>6859076</v>
+        <v>6859138</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B66" t="n">
-        <v>78709</v>
+        <v>79663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R66" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B67" t="n">
-        <v>79662</v>
+        <v>78710</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R67" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8191,7 +8191,7 @@
         <v>129197561</v>
       </c>
       <c r="B68" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>78051</v>
+        <v>78052</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8532,7 +8532,7 @@
         <v>129196543</v>
       </c>
       <c r="B71" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>129197157</v>
       </c>
       <c r="B72" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>129196431</v>
       </c>
       <c r="B73" t="n">
-        <v>78801</v>
+        <v>78802</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2267,46 +2267,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174816</v>
+        <v>129175174</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467140</v>
       </c>
       <c r="R16" t="n">
-        <v>6859054</v>
+        <v>6859092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174925</v>
+        <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,8 +2406,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466878</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6858977</v>
+        <v>6859054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,37 +2498,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129175174</v>
+        <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>98716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467140</v>
+        <v>466878</v>
       </c>
       <c r="R18" t="n">
-        <v>6859092</v>
+        <v>6858977</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
         <v>129174937</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>129174881</v>
       </c>
       <c r="B20" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3993,46 +3993,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129174795</v>
+        <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>98712</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4040,10 +4031,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467160</v>
+        <v>467077</v>
       </c>
       <c r="R31" t="n">
-        <v>6859063</v>
+        <v>6858882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4075,7 +4066,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4085,7 +4076,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4113,10 +4104,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174832</v>
+        <v>129174795</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4143,7 +4134,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4160,10 +4151,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467161</v>
+        <v>467160</v>
       </c>
       <c r="R32" t="n">
-        <v>6859044</v>
+        <v>6859063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,37 +4224,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129175713</v>
+        <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>98716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467077</v>
+        <v>467161</v>
       </c>
       <c r="R33" t="n">
-        <v>6858882</v>
+        <v>6859044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4347,7 +4347,7 @@
         <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,37 +4929,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129174718</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4967,10 +4968,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>467122</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6859101</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +5003,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5012,7 +5013,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5040,37 +5041,46 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129174751</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>98716</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5078,10 +5088,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>467131</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6859085</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5113,7 +5123,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5123,7 +5133,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5151,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175136</v>
+        <v>129175680</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5162,35 +5172,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5198,10 +5199,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467042</v>
+        <v>467104</v>
       </c>
       <c r="R41" t="n">
-        <v>6858941</v>
+        <v>6859032</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5233,7 +5234,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5243,7 +5244,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5252,6 +5253,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5270,38 +5272,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174718</v>
+        <v>129175685</v>
       </c>
       <c r="B42" t="n">
-        <v>98712</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5309,10 +5310,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467122</v>
+        <v>467096</v>
       </c>
       <c r="R42" t="n">
-        <v>6859101</v>
+        <v>6859018</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5344,7 +5345,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5354,7 +5355,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5382,46 +5383,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129174751</v>
+        <v>129175136</v>
       </c>
       <c r="B43" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5429,10 +5430,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467131</v>
+        <v>467042</v>
       </c>
       <c r="R43" t="n">
-        <v>6859085</v>
+        <v>6858941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5483,7 +5484,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>90171</v>
+        <v>90175</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7064,7 +7064,7 @@
         <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R59" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B60" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R60" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7405,7 +7405,7 @@
         <v>129196629</v>
       </c>
       <c r="B61" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R66" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R67" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8302,7 +8302,7 @@
         <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,44 +1231,36 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139492</v>
+        <v>129139418</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>97601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1278,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467077</v>
+        <v>467036</v>
       </c>
       <c r="R7" t="n">
-        <v>6858863</v>
+        <v>6858929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1351,36 +1343,44 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129139418</v>
+        <v>129139492</v>
       </c>
       <c r="B8" t="n">
-        <v>97593</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467036</v>
+        <v>467077</v>
       </c>
       <c r="R8" t="n">
-        <v>6858929</v>
+        <v>6858863</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>129174937</v>
       </c>
       <c r="B19" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>129174881</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3993,37 +3993,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129175713</v>
+        <v>129174795</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4031,10 +4040,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467077</v>
+        <v>467160</v>
       </c>
       <c r="R31" t="n">
-        <v>6858882</v>
+        <v>6859063</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4066,7 +4075,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4076,7 +4085,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4104,10 +4113,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174795</v>
+        <v>129174832</v>
       </c>
       <c r="B32" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4134,7 +4143,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4151,10 +4160,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467160</v>
+        <v>467161</v>
       </c>
       <c r="R32" t="n">
-        <v>6859063</v>
+        <v>6859044</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,46 +4233,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174832</v>
+        <v>129175713</v>
       </c>
       <c r="B33" t="n">
-        <v>98716</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467161</v>
+        <v>467077</v>
       </c>
       <c r="R33" t="n">
-        <v>6859044</v>
+        <v>6858882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4347,7 +4347,7 @@
         <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,38 +4929,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129174718</v>
+        <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4968,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467122</v>
+        <v>467104</v>
       </c>
       <c r="R39" t="n">
-        <v>6859101</v>
+        <v>6859032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5003,7 +5002,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5013,7 +5012,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5041,46 +5040,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129174751</v>
+        <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>98716</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5088,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467131</v>
+        <v>467096</v>
       </c>
       <c r="R40" t="n">
-        <v>6859085</v>
+        <v>6859018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5123,7 +5113,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5133,7 +5123,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5161,10 +5151,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175680</v>
+        <v>129175136</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5172,26 +5162,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5199,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467104</v>
+        <v>467042</v>
       </c>
       <c r="R41" t="n">
-        <v>6859032</v>
+        <v>6858941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5234,7 +5233,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5244,7 +5243,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5253,7 +5252,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5272,37 +5270,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129175685</v>
+        <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5310,10 +5309,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467096</v>
+        <v>467122</v>
       </c>
       <c r="R42" t="n">
-        <v>6859018</v>
+        <v>6859101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5345,7 +5344,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5355,7 +5354,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5383,46 +5382,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175136</v>
+        <v>129174751</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5430,10 +5429,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467042</v>
+        <v>467131</v>
       </c>
       <c r="R43" t="n">
-        <v>6858941</v>
+        <v>6859085</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5484,6 +5483,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6065,7 +6065,7 @@
         <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>90175</v>
+        <v>90176</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6950,36 +6950,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>92832</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6988,10 +6996,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R57" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7061,44 +7069,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B58" t="n">
-        <v>92831</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R58" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R59" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R60" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7405,7 +7405,7 @@
         <v>129196629</v>
       </c>
       <c r="B61" t="n">
-        <v>97587</v>
+        <v>97595</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129196543</v>
+        <v>129197157</v>
       </c>
       <c r="B71" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466877</v>
+        <v>466994</v>
       </c>
       <c r="R71" t="n">
-        <v>6859156</v>
+        <v>6859246</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129197157</v>
+        <v>129196543</v>
       </c>
       <c r="B72" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466994</v>
+        <v>466877</v>
       </c>
       <c r="R72" t="n">
-        <v>6859246</v>
+        <v>6859156</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,27 +1935,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R13" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,6 +2016,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,26 +2046,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R14" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2133,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129174937</v>
+        <v>129174881</v>
       </c>
       <c r="B19" t="n">
         <v>98724</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466864</v>
+        <v>467170</v>
       </c>
       <c r="R19" t="n">
-        <v>6858963</v>
+        <v>6859051</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,46 +2730,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129174881</v>
+        <v>129175206</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2777,10 +2768,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467170</v>
+        <v>466900</v>
       </c>
       <c r="R20" t="n">
-        <v>6859051</v>
+        <v>6858997</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129175206</v>
+        <v>129175049</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2861,26 +2852,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2888,10 +2880,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466900</v>
+        <v>466848</v>
       </c>
       <c r="R21" t="n">
-        <v>6858997</v>
+        <v>6858995</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,13 +2928,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2961,38 +2957,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129175049</v>
+        <v>129174937</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3000,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466848</v>
+        <v>466864</v>
       </c>
       <c r="R22" t="n">
-        <v>6858995</v>
+        <v>6858963</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,17 +3052,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3993,46 +3993,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129174795</v>
+        <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4040,10 +4031,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467160</v>
+        <v>467077</v>
       </c>
       <c r="R31" t="n">
-        <v>6859063</v>
+        <v>6858882</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4075,7 +4066,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4085,7 +4076,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4113,7 +4104,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174832</v>
+        <v>129174795</v>
       </c>
       <c r="B32" t="n">
         <v>98724</v>
@@ -4143,7 +4134,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4160,10 +4151,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467161</v>
+        <v>467160</v>
       </c>
       <c r="R32" t="n">
-        <v>6859044</v>
+        <v>6859063</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,37 +4224,46 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129175713</v>
+        <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>98724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467077</v>
+        <v>467161</v>
       </c>
       <c r="R33" t="n">
-        <v>6858882</v>
+        <v>6859044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129175136</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,26 +4940,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4967,10 +4976,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>467042</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6858941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +5011,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5012,7 +5021,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,7 +5030,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5040,37 +5048,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129174718</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5078,10 +5087,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>467122</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6859101</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5113,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5123,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5151,10 +5160,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175136</v>
+        <v>129175680</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5162,35 +5171,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467042</v>
+        <v>467104</v>
       </c>
       <c r="R41" t="n">
-        <v>6858941</v>
+        <v>6859032</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5252,6 +5252,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5270,38 +5271,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174718</v>
+        <v>129175685</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467122</v>
+        <v>467096</v>
       </c>
       <c r="R42" t="n">
-        <v>6859101</v>
+        <v>6859018</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6950,44 +6950,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B57" t="n">
-        <v>92832</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6996,10 +6988,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R57" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7069,36 +7061,44 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>92832</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R58" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7402,38 +7402,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B61" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7441,10 +7440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R61" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7471,22 +7470,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7514,37 +7513,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R62" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7744,10 +7744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197518</v>
+        <v>129197170</v>
       </c>
       <c r="B64" t="n">
-        <v>79634</v>
+        <v>78802</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466892</v>
+        <v>467020</v>
       </c>
       <c r="R64" t="n">
-        <v>6859076</v>
+        <v>6859138</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197170</v>
+        <v>129197518</v>
       </c>
       <c r="B65" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467020</v>
+        <v>466892</v>
       </c>
       <c r="R65" t="n">
-        <v>6859138</v>
+        <v>6859076</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B66" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R66" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B67" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R67" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8299,44 +8299,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B69" t="n">
-        <v>92832</v>
+        <v>78052</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8345,10 +8337,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R69" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,22 +8367,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8418,36 +8410,44 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B70" t="n">
-        <v>78052</v>
+        <v>92832</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R70" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8529,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197157</v>
+        <v>129196543</v>
       </c>
       <c r="B71" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466994</v>
+        <v>466877</v>
       </c>
       <c r="R71" t="n">
-        <v>6859246</v>
+        <v>6859156</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129196543</v>
+        <v>129197157</v>
       </c>
       <c r="B72" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466877</v>
+        <v>466994</v>
       </c>
       <c r="R72" t="n">
-        <v>6859156</v>
+        <v>6859246</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -1231,36 +1231,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139418</v>
+        <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>97601</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1270,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467036</v>
+        <v>467077</v>
       </c>
       <c r="R7" t="n">
-        <v>6858929</v>
+        <v>6858863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,44 +1351,36 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129139492</v>
+        <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>97601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467077</v>
+        <v>467036</v>
       </c>
       <c r="R8" t="n">
-        <v>6858863</v>
+        <v>6858929</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,26 +1935,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R13" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2022,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,27 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R14" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2132,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,37 +2267,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129175174</v>
+        <v>129174816</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467140</v>
+        <v>467156</v>
       </c>
       <c r="R16" t="n">
-        <v>6859092</v>
+        <v>6859054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174816</v>
+        <v>129174925</v>
       </c>
       <c r="B17" t="n">
         <v>98724</v>
@@ -2406,16 +2415,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>466878</v>
       </c>
       <c r="R17" t="n">
-        <v>6859054</v>
+        <v>6858977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,38 +2499,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129174925</v>
+        <v>129175174</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466878</v>
+        <v>467140</v>
       </c>
       <c r="R18" t="n">
-        <v>6858977</v>
+        <v>6859092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129174881</v>
+        <v>129174937</v>
       </c>
       <c r="B19" t="n">
         <v>98724</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467170</v>
+        <v>466864</v>
       </c>
       <c r="R19" t="n">
-        <v>6859051</v>
+        <v>6858963</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,37 +2730,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175206</v>
+        <v>129174881</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2768,10 +2777,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466900</v>
+        <v>467170</v>
       </c>
       <c r="R20" t="n">
-        <v>6858997</v>
+        <v>6859051</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,10 +2850,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129175049</v>
+        <v>129175206</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2852,27 +2861,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2880,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466848</v>
+        <v>466900</v>
       </c>
       <c r="R21" t="n">
-        <v>6858995</v>
+        <v>6858997</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,17 +2936,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2957,46 +2961,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174937</v>
+        <v>129175049</v>
       </c>
       <c r="B22" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +3000,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466864</v>
+        <v>466848</v>
       </c>
       <c r="R22" t="n">
-        <v>6858963</v>
+        <v>6858995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,13 +3048,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175136</v>
+        <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,35 +4940,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4976,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467042</v>
+        <v>467104</v>
       </c>
       <c r="R39" t="n">
-        <v>6858941</v>
+        <v>6859032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5011,7 +5002,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5021,7 +5012,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,6 +5021,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5048,38 +5040,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129174718</v>
+        <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5087,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467122</v>
+        <v>467096</v>
       </c>
       <c r="R40" t="n">
-        <v>6859101</v>
+        <v>6859018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5113,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5123,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5160,10 +5151,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175680</v>
+        <v>129175136</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5171,26 +5162,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467104</v>
+        <v>467042</v>
       </c>
       <c r="R41" t="n">
-        <v>6859032</v>
+        <v>6858941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5252,7 +5252,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5271,37 +5270,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129175685</v>
+        <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>98724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467096</v>
+        <v>467122</v>
       </c>
       <c r="R42" t="n">
-        <v>6859018</v>
+        <v>6859101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R66" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R67" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8529,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129196543</v>
+        <v>129197157</v>
       </c>
       <c r="B71" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466877</v>
+        <v>466994</v>
       </c>
       <c r="R71" t="n">
-        <v>6859156</v>
+        <v>6859246</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129197157</v>
+        <v>129196543</v>
       </c>
       <c r="B72" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466994</v>
+        <v>466877</v>
       </c>
       <c r="R72" t="n">
-        <v>6859246</v>
+        <v>6859156</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,27 +1935,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R13" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,6 +2016,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,26 +2046,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R14" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2133,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,46 +2267,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174816</v>
+        <v>129175174</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467140</v>
       </c>
       <c r="R16" t="n">
-        <v>6859054</v>
+        <v>6859092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174925</v>
+        <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2415,8 +2406,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466878</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6858977</v>
+        <v>6859054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,37 +2498,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129175174</v>
+        <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467140</v>
+        <v>466878</v>
       </c>
       <c r="R18" t="n">
-        <v>6859092</v>
+        <v>6858977</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,46 +2610,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129174937</v>
+        <v>129175206</v>
       </c>
       <c r="B19" t="n">
-        <v>98724</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2657,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466864</v>
+        <v>466900</v>
       </c>
       <c r="R19" t="n">
-        <v>6858963</v>
+        <v>6858997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,46 +2721,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129174881</v>
+        <v>129175049</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2777,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467170</v>
+        <v>466848</v>
       </c>
       <c r="R20" t="n">
-        <v>6859051</v>
+        <v>6858995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,13 +2808,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2850,37 +2837,46 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129175206</v>
+        <v>129174937</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2888,10 +2884,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466900</v>
+        <v>466864</v>
       </c>
       <c r="R21" t="n">
-        <v>6858997</v>
+        <v>6858963</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,38 +2957,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129175049</v>
+        <v>129174881</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3000,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466848</v>
+        <v>467170</v>
       </c>
       <c r="R22" t="n">
-        <v>6858995</v>
+        <v>6859051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,17 +3052,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129174795</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>129174751</v>
       </c>
       <c r="B43" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>90176</v>
+        <v>90178</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6950,36 +6950,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6988,10 +6996,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R57" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7061,44 +7069,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B58" t="n">
-        <v>92832</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R58" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7402,37 +7402,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7440,10 +7441,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R61" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,22 +7471,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7513,38 +7514,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B62" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R62" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197170</v>
+        <v>129197518</v>
       </c>
       <c r="B64" t="n">
-        <v>78802</v>
+        <v>79634</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467020</v>
+        <v>466892</v>
       </c>
       <c r="R64" t="n">
-        <v>6859138</v>
+        <v>6859076</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197518</v>
+        <v>129197170</v>
       </c>
       <c r="B65" t="n">
-        <v>79634</v>
+        <v>78802</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466892</v>
+        <v>467020</v>
       </c>
       <c r="R65" t="n">
-        <v>6859076</v>
+        <v>6859138</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B66" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R66" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B67" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R67" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8299,36 +8299,44 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>78052</v>
+        <v>92835</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8337,10 +8345,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R69" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8367,22 +8375,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8410,44 +8418,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>92832</v>
+        <v>78052</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R70" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8529,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129197157</v>
+        <v>129196543</v>
       </c>
       <c r="B71" t="n">
-        <v>78802</v>
+        <v>79663</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8540,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466994</v>
+        <v>466877</v>
       </c>
       <c r="R71" t="n">
-        <v>6859246</v>
+        <v>6859156</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8640,10 +8640,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129196543</v>
+        <v>129197157</v>
       </c>
       <c r="B72" t="n">
-        <v>79663</v>
+        <v>78802</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8651,21 +8651,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8678,10 +8678,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466877</v>
+        <v>466994</v>
       </c>
       <c r="R72" t="n">
-        <v>6859156</v>
+        <v>6859246</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,26 +1935,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R13" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2022,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,27 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R14" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2132,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,37 +2267,46 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129175174</v>
+        <v>129174816</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2314,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467140</v>
+        <v>467156</v>
       </c>
       <c r="R16" t="n">
-        <v>6859092</v>
+        <v>6859054</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,7 +2387,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174816</v>
+        <v>129174925</v>
       </c>
       <c r="B17" t="n">
         <v>98727</v>
@@ -2406,16 +2415,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2425,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>466878</v>
       </c>
       <c r="R17" t="n">
-        <v>6859054</v>
+        <v>6858977</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2498,38 +2499,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129174925</v>
+        <v>129175174</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466878</v>
+        <v>467140</v>
       </c>
       <c r="R18" t="n">
-        <v>6858977</v>
+        <v>6859092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129175685</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>467096</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6859018</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129175680</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -5078,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>467104</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6859032</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,27 +5513,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5541,10 +5540,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R44" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5576,7 +5575,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5586,12 +5585,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5600,6 +5594,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5618,10 +5613,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B45" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,26 +5624,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5656,10 +5652,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R45" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5691,7 +5687,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5701,7 +5697,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5710,7 +5711,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6950,44 +6950,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>79076</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6996,10 +6988,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R57" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7069,36 +7061,44 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>92835</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R58" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R59" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B60" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R60" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7966,10 +7966,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197086</v>
+        <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>79663</v>
+        <v>78710</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7977,21 +7977,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8004,10 +8004,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>466975</v>
+        <v>467039</v>
       </c>
       <c r="R66" t="n">
-        <v>6859149</v>
+        <v>6859234</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +8034,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,10 +8077,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197373</v>
+        <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>78710</v>
+        <v>79663</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8088,21 +8088,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8115,10 +8115,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>467039</v>
+        <v>466975</v>
       </c>
       <c r="R67" t="n">
-        <v>6859234</v>
+        <v>6859149</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8145,22 +8145,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,27 +1935,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R13" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,6 +2016,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,26 +2046,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R14" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2133,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2267,46 +2267,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129174816</v>
+        <v>129175174</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2314,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467156</v>
+        <v>467140</v>
       </c>
       <c r="R16" t="n">
-        <v>6859054</v>
+        <v>6859092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2387,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174925</v>
+        <v>129174816</v>
       </c>
       <c r="B17" t="n">
         <v>98727</v>
@@ -2415,8 +2406,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2426,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>466878</v>
+        <v>467156</v>
       </c>
       <c r="R17" t="n">
-        <v>6858977</v>
+        <v>6859054</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,37 +2498,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129175174</v>
+        <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467140</v>
+        <v>466878</v>
       </c>
       <c r="R18" t="n">
-        <v>6859092</v>
+        <v>6858977</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -4929,7 +4929,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175685</v>
+        <v>129175680</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467096</v>
+        <v>467104</v>
       </c>
       <c r="R39" t="n">
-        <v>6859018</v>
+        <v>6859032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175680</v>
+        <v>129175685</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -5078,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467104</v>
+        <v>467096</v>
       </c>
       <c r="R40" t="n">
-        <v>6859032</v>
+        <v>6859018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B54" t="n">
-        <v>78710</v>
+        <v>79123</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R54" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B55" t="n">
-        <v>79123</v>
+        <v>78710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R55" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7402,38 +7402,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B61" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7441,10 +7440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R61" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7471,22 +7470,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7514,37 +7513,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R62" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8299,44 +8299,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B69" t="n">
-        <v>92835</v>
+        <v>78052</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8345,10 +8337,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R69" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,22 +8367,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8418,36 +8410,44 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B70" t="n">
-        <v>78052</v>
+        <v>92835</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R70" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,26 +1935,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R13" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2022,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,27 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R14" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2132,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175206</v>
+        <v>129175049</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,26 +2621,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2648,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466900</v>
+        <v>466848</v>
       </c>
       <c r="R19" t="n">
-        <v>6858997</v>
+        <v>6858995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,13 +2697,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2721,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175049</v>
+        <v>129175206</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,27 +2737,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2760,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466848</v>
+        <v>466900</v>
       </c>
       <c r="R20" t="n">
-        <v>6858995</v>
+        <v>6858997</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,17 +2812,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129175136</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,26 +4940,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4967,10 +4976,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>467042</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6858941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +5011,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5012,7 +5021,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,7 +5030,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5040,7 +5048,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129175680</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -5078,10 +5086,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>467104</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6859032</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5151,10 +5159,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175136</v>
+        <v>129175685</v>
       </c>
       <c r="B41" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5162,35 +5170,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5198,10 +5197,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467042</v>
+        <v>467096</v>
       </c>
       <c r="R41" t="n">
-        <v>6858941</v>
+        <v>6859018</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5233,7 +5232,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5243,7 +5242,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5252,6 +5251,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B44" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,26 +5513,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5540,10 +5541,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R44" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5575,7 +5576,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5585,7 +5586,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,7 +5600,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5613,10 +5618,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,27 +5629,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5652,10 +5656,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R45" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5687,7 +5691,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,12 +5701,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,6 +5710,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B54" t="n">
-        <v>79123</v>
+        <v>78710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R54" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B55" t="n">
-        <v>78710</v>
+        <v>79123</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R55" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R59" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R60" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8299,36 +8299,44 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>78052</v>
+        <v>92835</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8337,10 +8345,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R69" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8367,22 +8375,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8410,44 +8418,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>92835</v>
+        <v>78052</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R70" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,27 +1935,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R13" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,6 +2016,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2035,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B14" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,26 +2046,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2078,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R14" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2113,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,7 +2133,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175049</v>
+        <v>129175206</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,27 +2621,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2649,10 +2648,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466848</v>
+        <v>466900</v>
       </c>
       <c r="R19" t="n">
-        <v>6858995</v>
+        <v>6858997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2697,17 +2696,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2726,37 +2721,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175206</v>
+        <v>129174937</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2764,10 +2768,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466900</v>
+        <v>466864</v>
       </c>
       <c r="R20" t="n">
-        <v>6858997</v>
+        <v>6858963</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2837,7 +2841,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174937</v>
+        <v>129174881</v>
       </c>
       <c r="B21" t="n">
         <v>98727</v>
@@ -2867,7 +2871,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2884,10 +2888,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466864</v>
+        <v>467170</v>
       </c>
       <c r="R21" t="n">
-        <v>6858963</v>
+        <v>6859051</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,46 +2961,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174881</v>
+        <v>129175049</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +3000,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467170</v>
+        <v>466848</v>
       </c>
       <c r="R22" t="n">
-        <v>6859051</v>
+        <v>6858995</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3052,13 +3048,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3188,37 +3188,46 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B24" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3226,10 +3235,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R24" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3299,46 +3308,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R25" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4344,46 +4344,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4391,10 +4382,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R34" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4417,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4427,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,37 +4455,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B35" t="n">
-        <v>78802</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R35" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175136</v>
+        <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,35 +4940,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4976,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467042</v>
+        <v>467104</v>
       </c>
       <c r="R39" t="n">
-        <v>6858941</v>
+        <v>6859032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5011,7 +5002,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5021,7 +5012,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,6 +5021,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5048,7 +5040,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175680</v>
+        <v>129175685</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -5086,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467104</v>
+        <v>467096</v>
       </c>
       <c r="R40" t="n">
-        <v>6859032</v>
+        <v>6859018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5159,37 +5151,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175685</v>
+        <v>129174751</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5197,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467096</v>
+        <v>467131</v>
       </c>
       <c r="R41" t="n">
-        <v>6859018</v>
+        <v>6859085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5232,7 +5233,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5242,7 +5243,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5382,46 +5383,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129174751</v>
+        <v>129175136</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5429,10 +5430,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467131</v>
+        <v>467042</v>
       </c>
       <c r="R43" t="n">
-        <v>6859085</v>
+        <v>6858941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5483,7 +5484,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B49" t="n">
-        <v>90178</v>
+        <v>78802</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R49" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B50" t="n">
-        <v>78802</v>
+        <v>90178</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R50" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B54" t="n">
-        <v>78710</v>
+        <v>79123</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R54" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B55" t="n">
-        <v>79123</v>
+        <v>78710</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R55" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7402,37 +7402,38 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7440,10 +7441,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R61" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,22 +7471,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7513,38 +7514,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B62" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R62" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8299,44 +8299,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B69" t="n">
-        <v>92835</v>
+        <v>78052</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8345,10 +8337,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R69" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,22 +8367,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8418,36 +8410,44 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B70" t="n">
-        <v>78052</v>
+        <v>92835</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R70" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -2721,46 +2721,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129174937</v>
+        <v>129175049</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2768,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466864</v>
+        <v>466848</v>
       </c>
       <c r="R20" t="n">
-        <v>6858963</v>
+        <v>6858995</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2816,13 +2808,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2961,38 +2957,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129175049</v>
+        <v>129174937</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3000,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466848</v>
+        <v>466864</v>
       </c>
       <c r="R22" t="n">
-        <v>6858995</v>
+        <v>6858963</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3048,17 +3052,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3188,46 +3188,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129174865</v>
+        <v>129175162</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>80185</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3235,10 +3226,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467191</v>
+        <v>467175</v>
       </c>
       <c r="R24" t="n">
-        <v>6859075</v>
+        <v>6859056</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,37 +3299,46 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129175162</v>
+        <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>80185</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467175</v>
+        <v>467191</v>
       </c>
       <c r="R25" t="n">
-        <v>6859056</v>
+        <v>6859075</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -4344,37 +4344,46 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129175650</v>
+        <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>78802</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4382,10 +4391,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466895</v>
+        <v>467141</v>
       </c>
       <c r="R34" t="n">
-        <v>6858952</v>
+        <v>6859072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4417,7 +4426,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4427,7 +4436,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,46 +4464,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129174783</v>
+        <v>129175650</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>78802</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4502,10 +4502,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467141</v>
+        <v>466895</v>
       </c>
       <c r="R35" t="n">
-        <v>6859072</v>
+        <v>6858952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4929,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129175136</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,26 +4940,35 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4967,10 +4976,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>467042</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6858941</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +5011,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5012,7 +5021,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,7 +5030,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5040,37 +5048,38 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129174718</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5078,10 +5087,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>467122</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6859101</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5113,7 +5122,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5123,7 +5132,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5271,38 +5280,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174718</v>
+        <v>129175680</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5310,10 +5318,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467122</v>
+        <v>467104</v>
       </c>
       <c r="R42" t="n">
-        <v>6859101</v>
+        <v>6859032</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5345,7 +5353,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5355,7 +5363,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5383,10 +5391,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175136</v>
+        <v>129175685</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5394,35 +5402,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5430,10 +5429,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467042</v>
+        <v>467096</v>
       </c>
       <c r="R43" t="n">
-        <v>6858941</v>
+        <v>6859018</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5465,7 +5464,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5475,7 +5474,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5484,6 +5483,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>78802</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,27 +5513,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5541,10 +5540,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R44" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5576,7 +5575,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5586,12 +5585,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5600,6 +5594,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5618,10 +5613,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B45" t="n">
-        <v>78802</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,26 +5624,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5656,10 +5652,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R45" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5691,7 +5687,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5701,7 +5697,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5710,7 +5711,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129196510</v>
+        <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>78802</v>
+        <v>90178</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4962</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>466862</v>
+        <v>467002</v>
       </c>
       <c r="R49" t="n">
-        <v>6859147</v>
+        <v>6859221</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +6130,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,10 +6173,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129197604</v>
+        <v>129196510</v>
       </c>
       <c r="B50" t="n">
-        <v>90178</v>
+        <v>78802</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4962</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6211,10 +6211,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467002</v>
+        <v>466862</v>
       </c>
       <c r="R50" t="n">
-        <v>6859221</v>
+        <v>6859147</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6241,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78710</v>
+        <v>78802</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78802</v>
+        <v>78710</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197281</v>
+        <v>129197410</v>
       </c>
       <c r="B54" t="n">
-        <v>79123</v>
+        <v>78710</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467009</v>
+        <v>467002</v>
       </c>
       <c r="R54" t="n">
-        <v>6859245</v>
+        <v>6859137</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6685,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,10 +6728,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197410</v>
+        <v>129197281</v>
       </c>
       <c r="B55" t="n">
-        <v>78710</v>
+        <v>79123</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6739,21 +6739,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467002</v>
+        <v>467009</v>
       </c>
       <c r="R55" t="n">
-        <v>6859137</v>
+        <v>6859245</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,22 +6796,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6950,36 +6950,44 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B57" t="n">
-        <v>79076</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6988,10 +6996,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R57" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7061,44 +7069,36 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B58" t="n">
-        <v>92835</v>
+        <v>79076</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R58" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8299,36 +8299,44 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B69" t="n">
-        <v>78052</v>
+        <v>92835</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8337,10 +8345,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R69" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8367,22 +8375,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8410,44 +8418,36 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B70" t="n">
-        <v>92835</v>
+        <v>78052</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R70" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129139219</v>
       </c>
       <c r="B2" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129138843</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>78827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129139522</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>129139476</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>129139538</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>129139492</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>129139418</v>
       </c>
       <c r="B8" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         <v>129139232</v>
       </c>
       <c r="B9" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>129139545</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>129175183</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175634</v>
+        <v>129175025</v>
       </c>
       <c r="B13" t="n">
-        <v>78802</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,26 +1935,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1962,10 +1963,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467082</v>
+        <v>467093</v>
       </c>
       <c r="R13" t="n">
-        <v>6859023</v>
+        <v>6859264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1997,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2008,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,7 +2022,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2035,10 +2040,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175025</v>
+        <v>129175634</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>78828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,27 +2051,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2074,10 +2078,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467093</v>
+        <v>467082</v>
       </c>
       <c r="R14" t="n">
-        <v>6859264</v>
+        <v>6859023</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,12 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,6 +2132,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>129175614</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>129175174</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>129174816</v>
       </c>
       <c r="B17" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129174925</v>
       </c>
       <c r="B18" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175206</v>
+        <v>129175049</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>57730</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,26 +2621,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2648,10 +2649,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466900</v>
+        <v>466848</v>
       </c>
       <c r="R19" t="n">
-        <v>6858997</v>
+        <v>6858995</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2696,13 +2697,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2721,10 +2726,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175049</v>
+        <v>129175206</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2732,27 +2737,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2760,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466848</v>
+        <v>466900</v>
       </c>
       <c r="R20" t="n">
-        <v>6858995</v>
+        <v>6858997</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2808,17 +2812,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174881</v>
+        <v>129174937</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467170</v>
+        <v>466864</v>
       </c>
       <c r="R21" t="n">
-        <v>6859051</v>
+        <v>6858963</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,10 +2957,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174937</v>
+        <v>129174881</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>466864</v>
+        <v>467170</v>
       </c>
       <c r="R22" t="n">
-        <v>6858963</v>
+        <v>6859051</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3080,7 +3080,7 @@
         <v>129175691</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129175162</v>
       </c>
       <c r="B24" t="n">
-        <v>80185</v>
+        <v>80211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>129174865</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>129174848</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>129174912</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>129175199</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>129174765</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>129175673</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>129175713</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>129174795</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>129174832</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         <v>129174783</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>129175650</v>
       </c>
       <c r="B35" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>129174896</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>129175151</v>
       </c>
       <c r="B37" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>129175792</v>
       </c>
       <c r="B38" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175136</v>
+        <v>129175680</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,35 +4940,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4976,10 +4967,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467042</v>
+        <v>467104</v>
       </c>
       <c r="R39" t="n">
-        <v>6858941</v>
+        <v>6859032</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5011,7 +5002,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5021,7 +5012,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5030,6 +5021,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5048,38 +5040,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129174718</v>
+        <v>129175685</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>79070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5087,10 +5078,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467122</v>
+        <v>467096</v>
       </c>
       <c r="R40" t="n">
-        <v>6859101</v>
+        <v>6859018</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5122,7 +5113,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5132,7 +5123,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5160,46 +5151,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129174751</v>
+        <v>129175136</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>57730</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5207,10 +5198,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467131</v>
+        <v>467042</v>
       </c>
       <c r="R41" t="n">
-        <v>6859085</v>
+        <v>6858941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5261,7 +5252,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5280,37 +5270,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129175680</v>
+        <v>129174718</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5318,10 +5309,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467104</v>
+        <v>467122</v>
       </c>
       <c r="R42" t="n">
-        <v>6859032</v>
+        <v>6859101</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5353,7 +5344,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5363,7 +5354,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5391,37 +5382,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175685</v>
+        <v>129174751</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>98756</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5429,10 +5429,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467096</v>
+        <v>467131</v>
       </c>
       <c r="R43" t="n">
-        <v>6859018</v>
+        <v>6859085</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B44" t="n">
-        <v>78802</v>
+        <v>57730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,26 +5513,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5540,10 +5541,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R44" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5575,7 +5576,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5585,7 +5586,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,7 +5600,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5613,10 +5618,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>78828</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,27 +5629,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5652,10 +5656,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R45" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5687,7 +5691,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,12 +5701,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,6 +5710,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>129196841</v>
       </c>
       <c r="B46" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>129197427</v>
       </c>
       <c r="B47" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>129197413</v>
       </c>
       <c r="B48" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>129197604</v>
       </c>
       <c r="B49" t="n">
-        <v>90178</v>
+        <v>90206</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>129196510</v>
       </c>
       <c r="B50" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>129196390</v>
       </c>
       <c r="B51" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>129197181</v>
       </c>
       <c r="B52" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>129196771</v>
       </c>
       <c r="B53" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>129197410</v>
       </c>
       <c r="B54" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         <v>129197281</v>
       </c>
       <c r="B55" t="n">
-        <v>79123</v>
+        <v>79149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         <v>129196497</v>
       </c>
       <c r="B56" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6950,44 +6950,36 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196354</v>
+        <v>129196589</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>79102</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
@@ -6996,10 +6988,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467132</v>
+        <v>466862</v>
       </c>
       <c r="R57" t="n">
-        <v>6858948</v>
+        <v>6859147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7069,36 +7061,44 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196589</v>
+        <v>129196354</v>
       </c>
       <c r="B58" t="n">
-        <v>79076</v>
+        <v>92863</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7107,10 +7107,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>466862</v>
+        <v>467132</v>
       </c>
       <c r="R58" t="n">
-        <v>6859147</v>
+        <v>6858948</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7183,7 +7183,7 @@
         <v>129197264</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>129196424</v>
       </c>
       <c r="B60" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7402,38 +7402,37 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129196629</v>
+        <v>129197648</v>
       </c>
       <c r="B61" t="n">
-        <v>97598</v>
+        <v>79070</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7441,10 +7440,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>466840</v>
+        <v>467131</v>
       </c>
       <c r="R61" t="n">
-        <v>6858994</v>
+        <v>6858952</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7471,22 +7470,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7514,37 +7513,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129197648</v>
+        <v>129196629</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>97627</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467131</v>
+        <v>466840</v>
       </c>
       <c r="R62" t="n">
-        <v>6858952</v>
+        <v>6858994</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7582,22 +7582,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7628,7 +7628,7 @@
         <v>129196342</v>
       </c>
       <c r="B63" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197518</v>
+        <v>129197170</v>
       </c>
       <c r="B64" t="n">
-        <v>79634</v>
+        <v>78828</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7755,21 +7755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>466892</v>
+        <v>467020</v>
       </c>
       <c r="R64" t="n">
-        <v>6859076</v>
+        <v>6859138</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7812,22 +7812,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,10 +7855,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197170</v>
+        <v>129197518</v>
       </c>
       <c r="B65" t="n">
-        <v>78802</v>
+        <v>79660</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7866,21 +7866,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467020</v>
+        <v>466892</v>
       </c>
       <c r="R65" t="n">
-        <v>6859138</v>
+        <v>6859076</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7923,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7969,7 +7969,7 @@
         <v>129197373</v>
       </c>
       <c r="B66" t="n">
-        <v>78710</v>
+        <v>78736</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
         <v>129197086</v>
       </c>
       <c r="B67" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>129197561</v>
       </c>
       <c r="B68" t="n">
-        <v>79634</v>
+        <v>79660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8299,44 +8299,36 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129196314</v>
+        <v>129197526</v>
       </c>
       <c r="B69" t="n">
-        <v>92835</v>
+        <v>78078</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8345,10 +8337,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466991</v>
+        <v>466892</v>
       </c>
       <c r="R69" t="n">
-        <v>6859197</v>
+        <v>6859076</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8375,22 +8367,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8418,36 +8410,44 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129197526</v>
+        <v>129196314</v>
       </c>
       <c r="B70" t="n">
-        <v>78052</v>
+        <v>92863</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466892</v>
+        <v>466991</v>
       </c>
       <c r="R70" t="n">
-        <v>6859076</v>
+        <v>6859197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8486,22 +8486,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8532,7 +8532,7 @@
         <v>129196543</v>
       </c>
       <c r="B71" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>129197157</v>
       </c>
       <c r="B72" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>129196431</v>
       </c>
       <c r="B73" t="n">
-        <v>78802</v>
+        <v>78828</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8860,6 +8860,307 @@
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129679926</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79070</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Sälsjöhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>467130</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6859193</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129679919</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Sälsjöhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>467173</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6859213</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129679923</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57730</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Sälsjöhållan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>466864</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6858989</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -4104,7 +4104,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174795</v>
+        <v>129174832</v>
       </c>
       <c r="B32" t="n">
         <v>98756</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4151,10 +4151,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467160</v>
+        <v>467161</v>
       </c>
       <c r="R32" t="n">
-        <v>6859063</v>
+        <v>6859044</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174832</v>
+        <v>129174795</v>
       </c>
       <c r="B33" t="n">
         <v>98756</v>
@@ -4254,7 +4254,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467161</v>
+        <v>467160</v>
       </c>
       <c r="R33" t="n">
-        <v>6859044</v>
+        <v>6859063</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5151,46 +5151,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175136</v>
+        <v>129174718</v>
       </c>
       <c r="B41" t="n">
-        <v>57730</v>
+        <v>98756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5198,10 +5190,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467042</v>
+        <v>467122</v>
       </c>
       <c r="R41" t="n">
-        <v>6858941</v>
+        <v>6859101</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5252,6 +5244,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5270,7 +5263,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174718</v>
+        <v>129174751</v>
       </c>
       <c r="B42" t="n">
         <v>98756</v>
@@ -5298,8 +5291,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5309,10 +5310,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467122</v>
+        <v>467131</v>
       </c>
       <c r="R42" t="n">
-        <v>6859101</v>
+        <v>6859085</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5382,46 +5383,46 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129174751</v>
+        <v>129175136</v>
       </c>
       <c r="B43" t="n">
-        <v>98756</v>
+        <v>57730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5429,10 +5430,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467131</v>
+        <v>467042</v>
       </c>
       <c r="R43" t="n">
-        <v>6859085</v>
+        <v>6858941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5483,7 +5484,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5502,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175069</v>
+        <v>129175662</v>
       </c>
       <c r="B44" t="n">
-        <v>57730</v>
+        <v>78828</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5513,27 +5513,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5541,10 +5540,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466837</v>
+        <v>466918</v>
       </c>
       <c r="R44" t="n">
-        <v>6858989</v>
+        <v>6858992</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5576,7 +5575,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5586,12 +5585,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spår av födosök på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5600,6 +5594,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5618,10 +5613,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175662</v>
+        <v>129175069</v>
       </c>
       <c r="B45" t="n">
-        <v>78828</v>
+        <v>57730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5629,26 +5624,27 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5656,10 +5652,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466918</v>
+        <v>466837</v>
       </c>
       <c r="R45" t="n">
-        <v>6858992</v>
+        <v>6858989</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5691,7 +5687,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5701,7 +5697,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5710,7 +5711,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -6395,10 +6395,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129197181</v>
+        <v>129196771</v>
       </c>
       <c r="B52" t="n">
-        <v>78828</v>
+        <v>78736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6406,21 +6406,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467027</v>
+        <v>467081</v>
       </c>
       <c r="R52" t="n">
-        <v>6859149</v>
+        <v>6859284</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6506,10 +6506,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129196771</v>
+        <v>129197181</v>
       </c>
       <c r="B53" t="n">
-        <v>78736</v>
+        <v>78828</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6517,21 +6517,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6544,10 +6544,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467081</v>
+        <v>467027</v>
       </c>
       <c r="R53" t="n">
-        <v>6859284</v>
+        <v>6859149</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7180,10 +7180,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129197264</v>
+        <v>129196424</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79689</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7191,21 +7191,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>466958</v>
+        <v>467042</v>
       </c>
       <c r="R59" t="n">
-        <v>6858988</v>
+        <v>6859027</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7291,10 +7291,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129196424</v>
+        <v>129197264</v>
       </c>
       <c r="B60" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7302,21 +7302,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467042</v>
+        <v>466958</v>
       </c>
       <c r="R60" t="n">
-        <v>6859027</v>
+        <v>6858988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8865,7 +8865,7 @@
         <v>129679926</v>
       </c>
       <c r="B74" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>129679919</v>
       </c>
       <c r="B75" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>129679923</v>
       </c>
       <c r="B76" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9160,6 +9160,107 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129758149</v>
+      </c>
+      <c r="B77" t="n">
+        <v>56916</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Stormyrbäcken, Hjd</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>466927</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6859020</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -8865,7 +8865,7 @@
         <v>129679926</v>
       </c>
       <c r="B74" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>129679919</v>
       </c>
       <c r="B75" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>129679923</v>
       </c>
       <c r="B76" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>129758149</v>
       </c>
       <c r="B77" t="n">
-        <v>56916</v>
+        <v>56917</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -8865,7 +8865,7 @@
         <v>129679926</v>
       </c>
       <c r="B74" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9262,6 +9262,1374 @@
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129803017</v>
+      </c>
+      <c r="B78" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>467115</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6859070</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129803033</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>467109</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6859093</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129803030</v>
+      </c>
+      <c r="B80" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>467112</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6859072</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129803023</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>466899</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6858960</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129803031</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>467113</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6859065</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129803025</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>466820</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6859174</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129803027</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>467096</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6859052</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129803021</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>467183</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6859085</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129803016</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>467100</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6859087</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129803029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>467101</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6859075</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129803032</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>467100</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6859092</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129803028</v>
+      </c>
+      <c r="B89" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>467092</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6859051</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129803026</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>467098</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6858924</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129803022</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98774</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Silvestica2, knärot, Hjd</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>466892</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6858962</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -9267,7 +9267,7 @@
         <v>129803017</v>
       </c>
       <c r="B78" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>129803033</v>
       </c>
       <c r="B79" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>129803030</v>
       </c>
       <c r="B80" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>129803023</v>
       </c>
       <c r="B81" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>129803031</v>
       </c>
       <c r="B82" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>129803025</v>
       </c>
       <c r="B83" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>129803027</v>
       </c>
       <c r="B84" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>129803021</v>
       </c>
       <c r="B85" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>129803016</v>
       </c>
       <c r="B86" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129803029</v>
       </c>
       <c r="B87" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>129803032</v>
       </c>
       <c r="B88" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>129803028</v>
       </c>
       <c r="B89" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>129803026</v>
       </c>
       <c r="B90" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129803022</v>
       </c>
       <c r="B91" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -9267,7 +9267,7 @@
         <v>129803017</v>
       </c>
       <c r="B78" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>129803033</v>
       </c>
       <c r="B79" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>129803030</v>
       </c>
       <c r="B80" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>129803023</v>
       </c>
       <c r="B81" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>129803031</v>
       </c>
       <c r="B82" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>129803025</v>
       </c>
       <c r="B83" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>129803027</v>
       </c>
       <c r="B84" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>129803021</v>
       </c>
       <c r="B85" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>129803016</v>
       </c>
       <c r="B86" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129803029</v>
       </c>
       <c r="B87" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>129803032</v>
       </c>
       <c r="B88" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>129803028</v>
       </c>
       <c r="B89" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>129803026</v>
       </c>
       <c r="B90" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129803022</v>
       </c>
       <c r="B91" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -9267,7 +9267,7 @@
         <v>129803017</v>
       </c>
       <c r="B78" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>129803033</v>
       </c>
       <c r="B79" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>129803030</v>
       </c>
       <c r="B80" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>129803023</v>
       </c>
       <c r="B81" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>129803031</v>
       </c>
       <c r="B82" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>129803025</v>
       </c>
       <c r="B83" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>129803027</v>
       </c>
       <c r="B84" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>129803021</v>
       </c>
       <c r="B85" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>129803016</v>
       </c>
       <c r="B86" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129803029</v>
       </c>
       <c r="B87" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>129803032</v>
       </c>
       <c r="B88" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>129803028</v>
       </c>
       <c r="B89" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>129803026</v>
       </c>
       <c r="B90" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129803022</v>
       </c>
       <c r="B91" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -9166,7 +9166,7 @@
         <v>129758149</v>
       </c>
       <c r="B77" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>129803017</v>
       </c>
       <c r="B78" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9366,10 +9366,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129803033</v>
+        <v>129803030</v>
       </c>
       <c r="B79" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>467109</v>
+        <v>467112</v>
       </c>
       <c r="R79" t="n">
-        <v>6859093</v>
+        <v>6859072</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9463,10 +9463,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129803030</v>
+        <v>129803033</v>
       </c>
       <c r="B80" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>467112</v>
+        <v>467109</v>
       </c>
       <c r="R80" t="n">
-        <v>6859072</v>
+        <v>6859093</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9563,7 +9563,7 @@
         <v>129803023</v>
       </c>
       <c r="B81" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>129803031</v>
       </c>
       <c r="B82" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129803025</v>
+        <v>129803027</v>
       </c>
       <c r="B83" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9789,10 +9789,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>466820</v>
+        <v>467096</v>
       </c>
       <c r="R83" t="n">
-        <v>6859174</v>
+        <v>6859052</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129803027</v>
+        <v>129803025</v>
       </c>
       <c r="B84" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9886,10 +9886,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>467096</v>
+        <v>466820</v>
       </c>
       <c r="R84" t="n">
-        <v>6859052</v>
+        <v>6859174</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9948,10 +9948,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129803021</v>
+        <v>129803016</v>
       </c>
       <c r="B85" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9976,17 +9976,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>467183</v>
+        <v>467100</v>
       </c>
       <c r="R85" t="n">
-        <v>6859085</v>
+        <v>6859087</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10027,6 +10031,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10045,10 +10050,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129803016</v>
+        <v>129803021</v>
       </c>
       <c r="B86" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10073,21 +10078,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>467100</v>
+        <v>467183</v>
       </c>
       <c r="R86" t="n">
-        <v>6859087</v>
+        <v>6859085</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -10128,7 +10129,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10150,7 +10150,7 @@
         <v>129803029</v>
       </c>
       <c r="B87" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>129803032</v>
       </c>
       <c r="B88" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>129803028</v>
       </c>
       <c r="B89" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>129803026</v>
       </c>
       <c r="B90" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129803022</v>
       </c>
       <c r="B91" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -8865,7 +8865,7 @@
         <v>129679926</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>129679919</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>129679923</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129803030</v>
+        <v>129803033</v>
       </c>
       <c r="B79" t="n">
         <v>98794</v>
@@ -9401,10 +9401,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>467112</v>
+        <v>467109</v>
       </c>
       <c r="R79" t="n">
-        <v>6859072</v>
+        <v>6859093</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9463,7 +9463,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129803033</v>
+        <v>129803030</v>
       </c>
       <c r="B80" t="n">
         <v>98794</v>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>467109</v>
+        <v>467112</v>
       </c>
       <c r="R80" t="n">
-        <v>6859093</v>
+        <v>6859072</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129803027</v>
+        <v>129803025</v>
       </c>
       <c r="B83" t="n">
         <v>98794</v>
@@ -9789,10 +9789,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>467096</v>
+        <v>466820</v>
       </c>
       <c r="R83" t="n">
-        <v>6859052</v>
+        <v>6859174</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9851,7 +9851,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129803025</v>
+        <v>129803027</v>
       </c>
       <c r="B84" t="n">
         <v>98794</v>
@@ -9886,10 +9886,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>466820</v>
+        <v>467096</v>
       </c>
       <c r="R84" t="n">
-        <v>6859174</v>
+        <v>6859052</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -9948,7 +9948,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129803016</v>
+        <v>129803021</v>
       </c>
       <c r="B85" t="n">
         <v>98794</v>
@@ -9976,21 +9976,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>467100</v>
+        <v>467183</v>
       </c>
       <c r="R85" t="n">
-        <v>6859087</v>
+        <v>6859085</v>
       </c>
       <c r="S85" t="n">
         <v>1</v>
@@ -10031,7 +10027,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10050,7 +10045,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129803021</v>
+        <v>129803016</v>
       </c>
       <c r="B86" t="n">
         <v>98794</v>
@@ -10078,17 +10073,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>467183</v>
+        <v>467100</v>
       </c>
       <c r="R86" t="n">
-        <v>6859085</v>
+        <v>6859087</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
@@ -10129,6 +10128,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -8865,7 +8865,7 @@
         <v>129679926</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>129679919</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>129679923</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>129758149</v>
       </c>
       <c r="B77" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>129803017</v>
       </c>
       <c r="B78" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>129803033</v>
       </c>
       <c r="B79" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>129803030</v>
       </c>
       <c r="B80" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>129803023</v>
       </c>
       <c r="B81" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9657,10 +9657,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129803031</v>
+        <v>129803025</v>
       </c>
       <c r="B82" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9692,10 +9692,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>467113</v>
+        <v>466820</v>
       </c>
       <c r="R82" t="n">
-        <v>6859065</v>
+        <v>6859174</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129803025</v>
+        <v>129803031</v>
       </c>
       <c r="B83" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9789,10 +9789,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>466820</v>
+        <v>467113</v>
       </c>
       <c r="R83" t="n">
-        <v>6859174</v>
+        <v>6859065</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9854,7 +9854,7 @@
         <v>129803027</v>
       </c>
       <c r="B84" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>129803021</v>
       </c>
       <c r="B85" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>129803016</v>
       </c>
       <c r="B86" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129803029</v>
       </c>
       <c r="B87" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>129803032</v>
       </c>
       <c r="B88" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>129803028</v>
       </c>
       <c r="B89" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>129803026</v>
       </c>
       <c r="B90" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129803022</v>
       </c>
       <c r="B91" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -8865,7 +8865,7 @@
         <v>129679926</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>129803017</v>
       </c>
       <c r="B78" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>129803033</v>
       </c>
       <c r="B79" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>129803030</v>
       </c>
       <c r="B80" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>129803023</v>
       </c>
       <c r="B81" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9657,10 +9657,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129803025</v>
+        <v>129803031</v>
       </c>
       <c r="B82" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9692,10 +9692,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>466820</v>
+        <v>467113</v>
       </c>
       <c r="R82" t="n">
-        <v>6859174</v>
+        <v>6859065</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9754,10 +9754,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129803031</v>
+        <v>129803025</v>
       </c>
       <c r="B83" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9789,10 +9789,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>467113</v>
+        <v>466820</v>
       </c>
       <c r="R83" t="n">
-        <v>6859065</v>
+        <v>6859174</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -9854,7 +9854,7 @@
         <v>129803027</v>
       </c>
       <c r="B84" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>129803021</v>
       </c>
       <c r="B85" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>129803016</v>
       </c>
       <c r="B86" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129803029</v>
       </c>
       <c r="B87" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>129803032</v>
       </c>
       <c r="B88" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>129803028</v>
       </c>
       <c r="B89" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>129803026</v>
       </c>
       <c r="B90" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129803022</v>
       </c>
       <c r="B91" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -8865,7 +8865,7 @@
         <v>129679926</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         <v>129803017</v>
       </c>
       <c r="B78" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>129803033</v>
       </c>
       <c r="B79" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>129803030</v>
       </c>
       <c r="B80" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>129803023</v>
       </c>
       <c r="B81" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>129803031</v>
       </c>
       <c r="B82" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>129803025</v>
       </c>
       <c r="B83" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>129803027</v>
       </c>
       <c r="B84" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>129803021</v>
       </c>
       <c r="B85" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>129803016</v>
       </c>
       <c r="B86" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129803029</v>
       </c>
       <c r="B87" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>129803032</v>
       </c>
       <c r="B88" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>129803028</v>
       </c>
       <c r="B89" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>129803026</v>
       </c>
       <c r="B90" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129803022</v>
       </c>
       <c r="B91" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -9657,7 +9657,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129803027</v>
+        <v>129803025</v>
       </c>
       <c r="B82" t="n">
         <v>98831</v>
@@ -9692,10 +9692,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>467096</v>
+        <v>466820</v>
       </c>
       <c r="R82" t="n">
-        <v>6859052</v>
+        <v>6859174</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9851,7 +9851,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129803025</v>
+        <v>129803027</v>
       </c>
       <c r="B84" t="n">
         <v>98831</v>
@@ -9886,10 +9886,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>466820</v>
+        <v>467096</v>
       </c>
       <c r="R84" t="n">
-        <v>6859174</v>
+        <v>6859052</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -9657,7 +9657,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129803025</v>
+        <v>129803031</v>
       </c>
       <c r="B82" t="n">
         <v>98831</v>
@@ -9692,10 +9692,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>466820</v>
+        <v>467113</v>
       </c>
       <c r="R82" t="n">
-        <v>6859174</v>
+        <v>6859065</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129803031</v>
+        <v>129803025</v>
       </c>
       <c r="B83" t="n">
         <v>98831</v>
@@ -9789,10 +9789,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>467113</v>
+        <v>466820</v>
       </c>
       <c r="R83" t="n">
-        <v>6859065</v>
+        <v>6859174</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -9267,7 +9267,7 @@
         <v>129803017</v>
       </c>
       <c r="B78" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>129803033</v>
       </c>
       <c r="B79" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>129803030</v>
       </c>
       <c r="B80" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>129803023</v>
       </c>
       <c r="B81" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>129803031</v>
       </c>
       <c r="B82" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>129803025</v>
       </c>
       <c r="B83" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>129803027</v>
       </c>
       <c r="B84" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>129803021</v>
       </c>
       <c r="B85" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>129803016</v>
       </c>
       <c r="B86" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>129803029</v>
       </c>
       <c r="B87" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>129803032</v>
       </c>
       <c r="B88" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>129803028</v>
       </c>
       <c r="B89" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>129803026</v>
       </c>
       <c r="B90" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>129803022</v>
       </c>
       <c r="B91" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129139219</v>
+        <v>129175174</v>
       </c>
       <c r="B2" t="n">
-        <v>78828</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467080</v>
+        <v>467140</v>
       </c>
       <c r="R2" t="n">
-        <v>6859021</v>
+        <v>6859092</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129138843</v>
+        <v>129175183</v>
       </c>
       <c r="B3" t="n">
-        <v>78827</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467061</v>
+        <v>466875</v>
       </c>
       <c r="R3" t="n">
-        <v>6859030</v>
+        <v>6859008</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +854,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,46 +897,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129139522</v>
+        <v>129175199</v>
       </c>
       <c r="B4" t="n">
-        <v>98756</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467078</v>
+        <v>466889</v>
       </c>
       <c r="R4" t="n">
-        <v>6858862</v>
+        <v>6859006</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,22 +965,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,38 +1008,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129139476</v>
+        <v>129175206</v>
       </c>
       <c r="B5" t="n">
-        <v>98756</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467031</v>
+        <v>466900</v>
       </c>
       <c r="R5" t="n">
-        <v>6858929</v>
+        <v>6858997</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,22 +1076,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,38 +1119,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129139538</v>
+        <v>129175713</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1161,7 +1160,7 @@
         <v>467077</v>
       </c>
       <c r="R6" t="n">
-        <v>6858856</v>
+        <v>6858882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,22 +1187,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,46 +1230,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129139492</v>
+        <v>129196589</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1278,10 +1268,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467077</v>
+        <v>466862</v>
       </c>
       <c r="R7" t="n">
-        <v>6858863</v>
+        <v>6859147</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,22 +1298,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,38 +1341,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129139418</v>
+        <v>129196771</v>
       </c>
       <c r="B8" t="n">
-        <v>97633</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1390,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467036</v>
+        <v>467081</v>
       </c>
       <c r="R8" t="n">
-        <v>6858929</v>
+        <v>6859284</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,22 +1409,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129139232</v>
+        <v>129197373</v>
       </c>
       <c r="B9" t="n">
-        <v>78828</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467100</v>
+        <v>467039</v>
       </c>
       <c r="R9" t="n">
-        <v>6859013</v>
+        <v>6859234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,22 +1520,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,46 +1563,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129139545</v>
+        <v>129197410</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1621,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467105</v>
+        <v>467002</v>
       </c>
       <c r="R10" t="n">
-        <v>6858853</v>
+        <v>6859137</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,22 +1631,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129175183</v>
+        <v>129197281</v>
       </c>
       <c r="B11" t="n">
-        <v>79102</v>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,21 +1685,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>466875</v>
+        <v>467009</v>
       </c>
       <c r="R11" t="n">
-        <v>6859008</v>
+        <v>6859245</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1767,7 +1747,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1777,7 +1757,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,11 +1788,11 @@
         <v>129175597</v>
       </c>
       <c r="B12" t="n">
-        <v>92863</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1924,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129175025</v>
+        <v>129175792</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,27 +1915,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1963,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467093</v>
+        <v>467058</v>
       </c>
       <c r="R13" t="n">
-        <v>6859264</v>
+        <v>6858890</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1998,7 +1985,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2008,12 +1995,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2022,6 +2004,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2040,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129175634</v>
+        <v>129196314</v>
       </c>
       <c r="B14" t="n">
-        <v>78828</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,25 +2034,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2078,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467082</v>
+        <v>466991</v>
       </c>
       <c r="R14" t="n">
-        <v>6859023</v>
+        <v>6859197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129175614</v>
+        <v>129196342</v>
       </c>
       <c r="B15" t="n">
-        <v>57890</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,27 +2153,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2190,10 +2188,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>466857</v>
+        <v>467015</v>
       </c>
       <c r="R15" t="n">
-        <v>6858979</v>
+        <v>6859188</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,17 +2236,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Noterat läte.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2267,10 +2261,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129175174</v>
+        <v>129196354</v>
       </c>
       <c r="B16" t="n">
-        <v>79102</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,25 +2272,33 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2305,10 +2307,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467140</v>
+        <v>467132</v>
       </c>
       <c r="R16" t="n">
-        <v>6859092</v>
+        <v>6858948</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2342,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2352,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,60 +2380,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129174816</v>
+        <v>129679931</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Sälsjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467156</v>
+        <v>467176</v>
       </c>
       <c r="R17" t="n">
-        <v>6859054</v>
+        <v>6859206</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2455,22 +2445,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,57 +2459,55 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129174925</v>
+        <v>129197604</v>
       </c>
       <c r="B18" t="n">
-        <v>98756</v>
+        <v>90522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>4962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2537,10 +2515,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>466878</v>
+        <v>467002</v>
       </c>
       <c r="R18" t="n">
-        <v>6858977</v>
+        <v>6859221</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,22 +2545,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129175049</v>
+        <v>129175708</v>
       </c>
       <c r="B19" t="n">
-        <v>57730</v>
+        <v>91930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,27 +2599,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2649,10 +2626,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>466848</v>
+        <v>467135</v>
       </c>
       <c r="R19" t="n">
-        <v>6858995</v>
+        <v>6858942</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2684,7 +2661,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,12 +2671,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,6 +2680,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2726,32 +2699,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129175206</v>
+        <v>129175673</v>
       </c>
       <c r="B20" t="n">
-        <v>79102</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2737,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>466900</v>
+        <v>467135</v>
       </c>
       <c r="R20" t="n">
-        <v>6858997</v>
+        <v>6859085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2799,7 +2772,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2782,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2810,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129174937</v>
+        <v>129175680</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,35 +2821,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2884,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>466864</v>
+        <v>467104</v>
       </c>
       <c r="R21" t="n">
-        <v>6858963</v>
+        <v>6859032</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2919,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2929,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,10 +2921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129174881</v>
+        <v>129175685</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2968,35 +2932,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3004,10 +2959,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467170</v>
+        <v>467096</v>
       </c>
       <c r="R22" t="n">
-        <v>6859051</v>
+        <v>6859018</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3080,11 +3035,11 @@
         <v>129175691</v>
       </c>
       <c r="B23" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3188,32 +3143,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129175162</v>
+        <v>129197207</v>
       </c>
       <c r="B24" t="n">
-        <v>80211</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3226,10 +3181,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467175</v>
+        <v>467010</v>
       </c>
       <c r="R24" t="n">
-        <v>6859056</v>
+        <v>6859296</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3261,7 +3216,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3271,7 +3226,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3299,10 +3254,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129174865</v>
+        <v>129197264</v>
       </c>
       <c r="B25" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,35 +3265,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3346,10 +3292,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467191</v>
+        <v>466958</v>
       </c>
       <c r="R25" t="n">
-        <v>6859075</v>
+        <v>6858988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3381,7 +3327,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3391,7 +3337,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3419,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129174848</v>
+        <v>129197648</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,27 +3376,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3458,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467183</v>
+        <v>467131</v>
       </c>
       <c r="R26" t="n">
-        <v>6859065</v>
+        <v>6858952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3488,22 +3433,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3531,10 +3476,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129174912</v>
+        <v>129679926</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,49 +3487,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Sälsjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
         <v>467130</v>
       </c>
       <c r="R27" t="n">
-        <v>6859021</v>
+        <v>6859193</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3608,22 +3541,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3632,70 +3555,66 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129175199</v>
+        <v>129679929</v>
       </c>
       <c r="B28" t="n">
-        <v>79102</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Sälsjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>466889</v>
+        <v>466824</v>
       </c>
       <c r="R28" t="n">
-        <v>6859006</v>
+        <v>6858999</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3719,22 +3638,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,65 +3652,55 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129174765</v>
+        <v>129138843</v>
       </c>
       <c r="B29" t="n">
-        <v>98756</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3809,10 +3708,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467126</v>
+        <v>467061</v>
       </c>
       <c r="R29" t="n">
-        <v>6859081</v>
+        <v>6859030</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3839,22 +3738,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3882,10 +3771,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129175673</v>
+        <v>129196424</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3893,21 +3782,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3920,10 +3809,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467135</v>
+        <v>467042</v>
       </c>
       <c r="R30" t="n">
-        <v>6859085</v>
+        <v>6859027</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3993,10 +3882,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129175713</v>
+        <v>129196543</v>
       </c>
       <c r="B31" t="n">
-        <v>79102</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4004,21 +3893,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4031,10 +3920,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467077</v>
+        <v>466877</v>
       </c>
       <c r="R31" t="n">
-        <v>6858882</v>
+        <v>6859156</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4104,46 +3993,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129174832</v>
+        <v>129196841</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4151,10 +4031,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467161</v>
+        <v>467081</v>
       </c>
       <c r="R32" t="n">
-        <v>6859044</v>
+        <v>6859284</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4186,7 +4066,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4196,7 +4076,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4224,46 +4104,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129174795</v>
+        <v>129197074</v>
       </c>
       <c r="B33" t="n">
-        <v>98756</v>
+        <v>79946</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4271,10 +4142,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>467160</v>
+        <v>466986</v>
       </c>
       <c r="R33" t="n">
-        <v>6859063</v>
+        <v>6859274</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4306,7 +4177,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4316,7 +4187,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4344,46 +4215,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129174783</v>
+        <v>129197086</v>
       </c>
       <c r="B34" t="n">
-        <v>98756</v>
+        <v>79946</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4391,10 +4253,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>467141</v>
+        <v>466975</v>
       </c>
       <c r="R34" t="n">
-        <v>6859072</v>
+        <v>6859149</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4288,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4436,7 +4298,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,10 +4326,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129175650</v>
+        <v>129197413</v>
       </c>
       <c r="B35" t="n">
-        <v>78828</v>
+        <v>79946</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4475,21 +4337,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4502,10 +4364,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>466895</v>
+        <v>467002</v>
       </c>
       <c r="R35" t="n">
-        <v>6858952</v>
+        <v>6859137</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4532,22 +4394,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4575,46 +4437,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129174896</v>
+        <v>129175162</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>80468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4622,10 +4475,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467147</v>
+        <v>467175</v>
       </c>
       <c r="R36" t="n">
-        <v>6859035</v>
+        <v>6859056</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4695,42 +4548,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129175151</v>
+        <v>129197526</v>
       </c>
       <c r="B37" t="n">
-        <v>57834</v>
+        <v>78334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4738,10 +4586,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466858</v>
+        <v>466892</v>
       </c>
       <c r="R37" t="n">
-        <v>6859162</v>
+        <v>6859076</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4768,22 +4616,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4792,6 +4640,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4810,45 +4659,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129175792</v>
+        <v>129175025</v>
       </c>
       <c r="B38" t="n">
-        <v>92863</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4856,10 +4698,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467058</v>
+        <v>467093</v>
       </c>
       <c r="R38" t="n">
-        <v>6858890</v>
+        <v>6859264</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4891,7 +4733,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4901,7 +4743,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4910,7 +4757,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4929,10 +4775,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175680</v>
+        <v>129175049</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4940,26 +4786,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4967,10 +4814,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>467104</v>
+        <v>466848</v>
       </c>
       <c r="R39" t="n">
-        <v>6859032</v>
+        <v>6858995</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5002,7 +4849,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5012,7 +4859,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5021,7 +4873,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5040,10 +4891,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175685</v>
+        <v>129175069</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5051,26 +4902,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5078,10 +4930,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>467096</v>
+        <v>466837</v>
       </c>
       <c r="R40" t="n">
-        <v>6859018</v>
+        <v>6858989</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5113,7 +4965,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5123,7 +4975,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5132,7 +4989,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5151,38 +5007,46 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129174718</v>
+        <v>129175136</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5190,10 +5054,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467122</v>
+        <v>467042</v>
       </c>
       <c r="R41" t="n">
-        <v>6859101</v>
+        <v>6858941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5244,7 +5108,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5263,60 +5126,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129174751</v>
+        <v>129679919</v>
       </c>
       <c r="B42" t="n">
-        <v>98756</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Sälsjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467131</v>
+        <v>467173</v>
       </c>
       <c r="R42" t="n">
-        <v>6859085</v>
+        <v>6859213</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5340,22 +5191,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5364,29 +5210,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129175136</v>
+        <v>129679923</v>
       </c>
       <c r="B43" t="n">
-        <v>57730</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5411,32 +5256,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Sälsjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>467042</v>
+        <v>466864</v>
       </c>
       <c r="R43" t="n">
-        <v>6858941</v>
+        <v>6858989</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5460,22 +5293,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5490,63 +5318,64 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129175662</v>
+        <v>129758149</v>
       </c>
       <c r="B44" t="n">
-        <v>78828</v>
+        <v>57132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stormyrbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466918</v>
+        <v>466927</v>
       </c>
       <c r="R44" t="n">
-        <v>6858992</v>
+        <v>6859020</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5570,22 +5399,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,29 +5413,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175069</v>
+        <v>129175614</v>
       </c>
       <c r="B45" t="n">
-        <v>57730</v>
+        <v>58114</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5624,21 +5442,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5652,10 +5470,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466837</v>
+        <v>466857</v>
       </c>
       <c r="R45" t="n">
-        <v>6858989</v>
+        <v>6858979</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5687,7 +5505,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,12 +5515,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Spår av födosök på gran.</t>
+          <t>Noterat läte.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5729,10 +5547,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129196841</v>
+        <v>129175151</v>
       </c>
       <c r="B46" t="n">
-        <v>79689</v>
+        <v>58057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5740,26 +5558,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5767,10 +5590,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>467081</v>
+        <v>466858</v>
       </c>
       <c r="R46" t="n">
-        <v>6859284</v>
+        <v>6859162</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5802,7 +5625,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5812,7 +5635,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5821,7 +5644,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5840,10 +5662,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129197427</v>
+        <v>129281334</v>
       </c>
       <c r="B47" t="n">
-        <v>79660</v>
+        <v>58057</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5851,26 +5673,31 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5878,10 +5705,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>467058</v>
+        <v>466961</v>
       </c>
       <c r="R47" t="n">
-        <v>6859193</v>
+        <v>6859064</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5908,22 +5735,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5932,7 +5759,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5951,37 +5777,38 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129197413</v>
+        <v>129139476</v>
       </c>
       <c r="B48" t="n">
-        <v>79689</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5989,10 +5816,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467002</v>
+        <v>467031</v>
       </c>
       <c r="R48" t="n">
-        <v>6859137</v>
+        <v>6858929</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6019,22 +5846,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6062,37 +5889,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129197604</v>
+        <v>129139492</v>
       </c>
       <c r="B49" t="n">
-        <v>90206</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6100,10 +5936,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467002</v>
+        <v>467077</v>
       </c>
       <c r="R49" t="n">
-        <v>6859221</v>
+        <v>6858863</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6130,22 +5966,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6173,37 +6009,46 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129196510</v>
+        <v>129139507</v>
       </c>
       <c r="B50" t="n">
-        <v>78828</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6211,10 +6056,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>466862</v>
+        <v>467063</v>
       </c>
       <c r="R50" t="n">
-        <v>6859147</v>
+        <v>6858862</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6241,22 +6086,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6284,37 +6129,46 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129196390</v>
+        <v>129139522</v>
       </c>
       <c r="B51" t="n">
-        <v>78828</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6322,10 +6176,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467022</v>
+        <v>467078</v>
       </c>
       <c r="R51" t="n">
-        <v>6859109</v>
+        <v>6858862</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6352,22 +6206,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6395,37 +6249,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129196771</v>
+        <v>129139527</v>
       </c>
       <c r="B52" t="n">
-        <v>78736</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6433,10 +6296,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467081</v>
+        <v>467072</v>
       </c>
       <c r="R52" t="n">
-        <v>6859284</v>
+        <v>6858857</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6463,22 +6326,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6506,37 +6369,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129197181</v>
+        <v>129139538</v>
       </c>
       <c r="B53" t="n">
-        <v>78828</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6544,10 +6408,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467027</v>
+        <v>467077</v>
       </c>
       <c r="R53" t="n">
-        <v>6859149</v>
+        <v>6858856</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6574,22 +6438,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6617,37 +6481,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129197410</v>
+        <v>129139545</v>
       </c>
       <c r="B54" t="n">
-        <v>78736</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6655,10 +6528,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467002</v>
+        <v>467105</v>
       </c>
       <c r="R54" t="n">
-        <v>6859137</v>
+        <v>6858853</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6685,22 +6558,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6728,37 +6601,38 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129197281</v>
+        <v>129174718</v>
       </c>
       <c r="B55" t="n">
-        <v>79149</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>864</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6766,10 +6640,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467009</v>
+        <v>467122</v>
       </c>
       <c r="R55" t="n">
-        <v>6859245</v>
+        <v>6859101</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6801,7 +6675,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6811,7 +6685,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6839,37 +6713,46 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129196497</v>
+        <v>129174751</v>
       </c>
       <c r="B56" t="n">
-        <v>78828</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6877,10 +6760,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>466875</v>
+        <v>467131</v>
       </c>
       <c r="R56" t="n">
-        <v>6859133</v>
+        <v>6859085</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6912,7 +6795,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6922,7 +6805,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6950,37 +6833,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129196589</v>
+        <v>129174765</v>
       </c>
       <c r="B57" t="n">
-        <v>79102</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6988,10 +6880,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>466862</v>
+        <v>467126</v>
       </c>
       <c r="R57" t="n">
-        <v>6859147</v>
+        <v>6859081</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7023,7 +6915,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7033,7 +6925,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7061,45 +6953,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129196354</v>
+        <v>129174783</v>
       </c>
       <c r="B58" t="n">
-        <v>92863</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7107,10 +7000,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467132</v>
+        <v>467141</v>
       </c>
       <c r="R58" t="n">
-        <v>6858948</v>
+        <v>6859072</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7142,7 +7035,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7152,7 +7045,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7180,37 +7073,46 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129196424</v>
+        <v>129174795</v>
       </c>
       <c r="B59" t="n">
-        <v>79689</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7218,10 +7120,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467042</v>
+        <v>467160</v>
       </c>
       <c r="R59" t="n">
-        <v>6859027</v>
+        <v>6859063</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7253,7 +7155,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7263,7 +7165,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7291,37 +7193,46 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129197264</v>
+        <v>129174816</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7329,10 +7240,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>466958</v>
+        <v>467156</v>
       </c>
       <c r="R60" t="n">
-        <v>6858988</v>
+        <v>6859054</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7364,7 +7275,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7374,7 +7285,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7402,37 +7313,46 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129197648</v>
+        <v>129174832</v>
       </c>
       <c r="B61" t="n">
-        <v>79070</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7440,10 +7360,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467131</v>
+        <v>467161</v>
       </c>
       <c r="R61" t="n">
-        <v>6858952</v>
+        <v>6859044</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7470,22 +7390,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7513,32 +7433,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129196629</v>
+        <v>129174848</v>
       </c>
       <c r="B62" t="n">
-        <v>97627</v>
+        <v>99118</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7552,10 +7472,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>466840</v>
+        <v>467183</v>
       </c>
       <c r="R62" t="n">
-        <v>6858994</v>
+        <v>6859065</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7587,7 +7507,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7597,7 +7517,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7625,45 +7545,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129196342</v>
+        <v>129174865</v>
       </c>
       <c r="B63" t="n">
-        <v>92863</v>
+        <v>99118</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7671,10 +7592,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467015</v>
+        <v>467191</v>
       </c>
       <c r="R63" t="n">
-        <v>6859188</v>
+        <v>6859075</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7706,7 +7627,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7716,7 +7637,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7744,37 +7665,46 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129197170</v>
+        <v>129174881</v>
       </c>
       <c r="B64" t="n">
-        <v>78828</v>
+        <v>99118</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7782,10 +7712,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467020</v>
+        <v>467170</v>
       </c>
       <c r="R64" t="n">
-        <v>6859138</v>
+        <v>6859051</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7817,7 +7747,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7827,7 +7757,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7855,37 +7785,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129197518</v>
+        <v>129174896</v>
       </c>
       <c r="B65" t="n">
-        <v>79660</v>
+        <v>99118</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7893,10 +7832,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>466892</v>
+        <v>467147</v>
       </c>
       <c r="R65" t="n">
-        <v>6859076</v>
+        <v>6859035</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7923,22 +7862,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7966,37 +7905,46 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129197373</v>
+        <v>129174912</v>
       </c>
       <c r="B66" t="n">
-        <v>78736</v>
+        <v>99118</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8004,10 +7952,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467039</v>
+        <v>467130</v>
       </c>
       <c r="R66" t="n">
-        <v>6859234</v>
+        <v>6859021</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8034,22 +7982,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8077,37 +8025,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129197086</v>
+        <v>129174925</v>
       </c>
       <c r="B67" t="n">
-        <v>79689</v>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8115,10 +8064,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466975</v>
+        <v>466878</v>
       </c>
       <c r="R67" t="n">
-        <v>6859149</v>
+        <v>6858977</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8150,7 +8099,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8160,7 +8109,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8188,37 +8137,46 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129197561</v>
+        <v>129174937</v>
       </c>
       <c r="B68" t="n">
-        <v>79660</v>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8226,10 +8184,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466891</v>
+        <v>466864</v>
       </c>
       <c r="R68" t="n">
-        <v>6859119</v>
+        <v>6858963</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8256,22 +8214,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8299,51 +8257,52 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129197526</v>
+        <v>129803016</v>
       </c>
       <c r="B69" t="n">
-        <v>78078</v>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>466892</v>
+        <v>467100</v>
       </c>
       <c r="R69" t="n">
-        <v>6859076</v>
+        <v>6859087</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8367,22 +8326,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>21:36</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>21:36</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8398,71 +8347,64 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129196314</v>
+        <v>129803017</v>
       </c>
       <c r="B70" t="n">
-        <v>92863</v>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>466991</v>
+        <v>467115</v>
       </c>
       <c r="R70" t="n">
-        <v>6859197</v>
+        <v>6859070</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8486,22 +8428,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8517,63 +8449,60 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129196543</v>
+        <v>129803021</v>
       </c>
       <c r="B71" t="n">
-        <v>79689</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>466877</v>
+        <v>467183</v>
       </c>
       <c r="R71" t="n">
-        <v>6859156</v>
+        <v>6859085</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8597,22 +8526,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8621,70 +8540,66 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129197157</v>
+        <v>129803022</v>
       </c>
       <c r="B72" t="n">
-        <v>78828</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466994</v>
+        <v>466892</v>
       </c>
       <c r="R72" t="n">
-        <v>6859246</v>
+        <v>6858962</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8708,22 +8623,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8732,70 +8637,66 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129196431</v>
+        <v>129803023</v>
       </c>
       <c r="B73" t="n">
-        <v>78828</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>467059</v>
+        <v>466899</v>
       </c>
       <c r="R73" t="n">
-        <v>6859031</v>
+        <v>6858960</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8819,22 +8720,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8843,64 +8734,63 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129679926</v>
+        <v>129803025</v>
       </c>
       <c r="B74" t="n">
-        <v>79089</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sälsjöhållan, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>467130</v>
+        <v>466820</v>
       </c>
       <c r="R74" t="n">
-        <v>6859193</v>
+        <v>6859174</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8959,45 +8849,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129679919</v>
+        <v>129803026</v>
       </c>
       <c r="B75" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Sälsjöhållan, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>467173</v>
+        <v>467098</v>
       </c>
       <c r="R75" t="n">
-        <v>6859213</v>
+        <v>6858924</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -9030,11 +8920,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9061,45 +8946,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129679923</v>
+        <v>129803027</v>
       </c>
       <c r="B76" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sälsjöhållan, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>466864</v>
+        <v>467096</v>
       </c>
       <c r="R76" t="n">
-        <v>6858989</v>
+        <v>6859052</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -9132,11 +9017,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9163,52 +9043,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129758149</v>
+        <v>129803028</v>
       </c>
       <c r="B77" t="n">
-        <v>56922</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stormyrbäcken, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>466927</v>
+        <v>467092</v>
       </c>
       <c r="R77" t="n">
-        <v>6859020</v>
+        <v>6859051</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9232,12 +9108,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9252,22 +9128,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129803017</v>
+        <v>129803029</v>
       </c>
       <c r="B78" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9292,21 +9168,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>467115</v>
+        <v>467101</v>
       </c>
       <c r="R78" t="n">
-        <v>6859070</v>
+        <v>6859075</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -9347,7 +9219,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9366,10 +9237,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129803033</v>
+        <v>129803030</v>
       </c>
       <c r="B79" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9401,10 +9272,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>467109</v>
+        <v>467112</v>
       </c>
       <c r="R79" t="n">
-        <v>6859093</v>
+        <v>6859072</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9463,10 +9334,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129803030</v>
+        <v>129803031</v>
       </c>
       <c r="B80" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9498,10 +9369,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>467112</v>
+        <v>467113</v>
       </c>
       <c r="R80" t="n">
-        <v>6859072</v>
+        <v>6859065</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9560,10 +9431,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129803023</v>
+        <v>129803032</v>
       </c>
       <c r="B81" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9595,10 +9466,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>466899</v>
+        <v>467100</v>
       </c>
       <c r="R81" t="n">
-        <v>6858960</v>
+        <v>6859092</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9657,10 +9528,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129803031</v>
+        <v>129803033</v>
       </c>
       <c r="B82" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9692,10 +9563,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>467113</v>
+        <v>467109</v>
       </c>
       <c r="R82" t="n">
-        <v>6859065</v>
+        <v>6859093</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9754,48 +9625,52 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129803025</v>
+        <v>129139418</v>
       </c>
       <c r="B83" t="n">
-        <v>98833</v>
+        <v>97989</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>466820</v>
+        <v>467036</v>
       </c>
       <c r="R83" t="n">
-        <v>6859174</v>
+        <v>6858929</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9819,12 +9694,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9833,66 +9718,71 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129803027</v>
+        <v>129196629</v>
       </c>
       <c r="B84" t="n">
-        <v>98833</v>
+        <v>97983</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>467096</v>
+        <v>466840</v>
       </c>
       <c r="R84" t="n">
-        <v>6859052</v>
+        <v>6858994</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9916,12 +9806,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9930,66 +9830,70 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129803021</v>
+        <v>129139219</v>
       </c>
       <c r="B85" t="n">
-        <v>98833</v>
+        <v>79085</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>467183</v>
+        <v>467080</v>
       </c>
       <c r="R85" t="n">
-        <v>6859085</v>
+        <v>6859021</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10013,12 +9917,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10027,70 +9941,70 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129803016</v>
+        <v>129139232</v>
       </c>
       <c r="B86" t="n">
-        <v>98833</v>
+        <v>79085</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q86" t="n">
         <v>467100</v>
       </c>
       <c r="R86" t="n">
-        <v>6859087</v>
+        <v>6859013</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10114,12 +10028,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10135,60 +10059,63 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129803029</v>
+        <v>129175634</v>
       </c>
       <c r="B87" t="n">
-        <v>98833</v>
+        <v>79085</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>467101</v>
+        <v>467082</v>
       </c>
       <c r="R87" t="n">
-        <v>6859075</v>
+        <v>6859023</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10212,12 +10139,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10226,66 +10163,70 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129803032</v>
+        <v>129175650</v>
       </c>
       <c r="B88" t="n">
-        <v>98833</v>
+        <v>79085</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>467100</v>
+        <v>466895</v>
       </c>
       <c r="R88" t="n">
-        <v>6859092</v>
+        <v>6858952</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10309,12 +10250,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10323,66 +10274,70 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129803028</v>
+        <v>129175662</v>
       </c>
       <c r="B89" t="n">
-        <v>98833</v>
+        <v>79085</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>467092</v>
+        <v>466918</v>
       </c>
       <c r="R89" t="n">
-        <v>6859051</v>
+        <v>6858992</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10406,12 +10361,22 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10420,66 +10385,70 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129803026</v>
+        <v>129196390</v>
       </c>
       <c r="B90" t="n">
-        <v>98833</v>
+        <v>79085</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>467098</v>
+        <v>467022</v>
       </c>
       <c r="R90" t="n">
-        <v>6858924</v>
+        <v>6859109</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10503,12 +10472,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10517,66 +10496,70 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129803022</v>
+        <v>129196431</v>
       </c>
       <c r="B91" t="n">
-        <v>98833</v>
+        <v>79085</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>466892</v>
+        <v>467059</v>
       </c>
       <c r="R91" t="n">
-        <v>6858962</v>
+        <v>6859031</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10600,12 +10583,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10614,21 +10607,910 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129196497</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>466875</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6859133</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129196510</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>466862</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6859147</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129197157</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>466994</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6859246</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129197170</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>467020</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6859138</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129197181</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>467027</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6859149</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129197427</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>467058</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6859193</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129197518</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>466892</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6859076</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129197561</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>466891</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6859119</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3670,10 +3670,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129138843</v>
+        <v>134672969</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>83358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3681,40 +3681,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stor-Svarttjärnen, Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467061</v>
+        <v>466846</v>
       </c>
       <c r="R29" t="n">
-        <v>6859030</v>
+        <v>6858944</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3738,12 +3735,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3752,7 +3749,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3771,10 +3767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129196424</v>
+        <v>129138843</v>
       </c>
       <c r="B30" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,21 +3778,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3809,10 +3805,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467042</v>
+        <v>467061</v>
       </c>
       <c r="R30" t="n">
-        <v>6859027</v>
+        <v>6859030</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3839,22 +3835,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3882,7 +3868,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129196543</v>
+        <v>129196424</v>
       </c>
       <c r="B31" t="n">
         <v>79946</v>
@@ -3920,10 +3906,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>466877</v>
+        <v>467042</v>
       </c>
       <c r="R31" t="n">
-        <v>6859156</v>
+        <v>6859027</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3993,7 +3979,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129196841</v>
+        <v>129196543</v>
       </c>
       <c r="B32" t="n">
         <v>79946</v>
@@ -4031,10 +4017,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>467081</v>
+        <v>466877</v>
       </c>
       <c r="R32" t="n">
-        <v>6859284</v>
+        <v>6859156</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4104,7 +4090,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129197074</v>
+        <v>129196841</v>
       </c>
       <c r="B33" t="n">
         <v>79946</v>
@@ -4142,10 +4128,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>466986</v>
+        <v>467081</v>
       </c>
       <c r="R33" t="n">
-        <v>6859274</v>
+        <v>6859284</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4215,7 +4201,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129197086</v>
+        <v>129197074</v>
       </c>
       <c r="B34" t="n">
         <v>79946</v>
@@ -4253,10 +4239,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>466975</v>
+        <v>466986</v>
       </c>
       <c r="R34" t="n">
-        <v>6859149</v>
+        <v>6859274</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4326,7 +4312,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129197413</v>
+        <v>129197086</v>
       </c>
       <c r="B35" t="n">
         <v>79946</v>
@@ -4364,10 +4350,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>467002</v>
+        <v>466975</v>
       </c>
       <c r="R35" t="n">
-        <v>6859137</v>
+        <v>6859149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4394,22 +4380,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4437,32 +4423,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129175162</v>
+        <v>129197413</v>
       </c>
       <c r="B36" t="n">
-        <v>80468</v>
+        <v>79946</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4475,10 +4461,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>467175</v>
+        <v>467002</v>
       </c>
       <c r="R36" t="n">
-        <v>6859056</v>
+        <v>6859137</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4505,22 +4491,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4548,32 +4534,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129197526</v>
+        <v>129175162</v>
       </c>
       <c r="B37" t="n">
-        <v>78334</v>
+        <v>80468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4586,10 +4572,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>466892</v>
+        <v>467175</v>
       </c>
       <c r="R37" t="n">
-        <v>6859076</v>
+        <v>6859056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4616,22 +4602,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4659,10 +4645,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129175025</v>
+        <v>129197526</v>
       </c>
       <c r="B38" t="n">
-        <v>57953</v>
+        <v>78334</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4670,27 +4656,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4698,10 +4683,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>467093</v>
+        <v>466892</v>
       </c>
       <c r="R38" t="n">
-        <v>6859264</v>
+        <v>6859076</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4728,27 +4713,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4757,6 +4737,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4775,7 +4756,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129175049</v>
+        <v>129175025</v>
       </c>
       <c r="B39" t="n">
         <v>57953</v>
@@ -4814,10 +4795,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>466848</v>
+        <v>467093</v>
       </c>
       <c r="R39" t="n">
-        <v>6858995</v>
+        <v>6859264</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4864,7 +4845,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran.</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4891,7 +4872,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129175069</v>
+        <v>129175049</v>
       </c>
       <c r="B40" t="n">
         <v>57953</v>
@@ -4930,10 +4911,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>466837</v>
+        <v>466848</v>
       </c>
       <c r="R40" t="n">
-        <v>6858989</v>
+        <v>6858995</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4980,7 +4961,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spår av födosök på gran.</t>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5007,7 +4988,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129175136</v>
+        <v>129175069</v>
       </c>
       <c r="B41" t="n">
         <v>57953</v>
@@ -5035,17 +5016,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
@@ -5054,10 +5027,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>467042</v>
+        <v>466837</v>
       </c>
       <c r="R41" t="n">
-        <v>6858941</v>
+        <v>6858989</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5100,6 +5073,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Spår av födosök på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5126,7 +5104,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129679919</v>
+        <v>129175136</v>
       </c>
       <c r="B42" t="n">
         <v>57953</v>
@@ -5154,20 +5132,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sälsjöhållan, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>467173</v>
+        <v>467042</v>
       </c>
       <c r="R42" t="n">
-        <v>6859213</v>
+        <v>6858941</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5191,17 +5181,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5216,19 +5211,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129679923</v>
+        <v>129679919</v>
       </c>
       <c r="B43" t="n">
         <v>57953</v>
@@ -5263,10 +5258,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>466864</v>
+        <v>467173</v>
       </c>
       <c r="R43" t="n">
-        <v>6858989</v>
+        <v>6859213</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5303,7 +5298,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5330,27 +5325,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129758149</v>
+        <v>129679923</v>
       </c>
       <c r="B44" t="n">
-        <v>57132</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5359,23 +5354,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stormyrbäcken, Hjd</t>
+          <t>Sälsjöhållan, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>466927</v>
+        <v>466864</v>
       </c>
       <c r="R44" t="n">
-        <v>6859020</v>
+        <v>6858989</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5399,12 +5390,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5419,44 +5415,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129175614</v>
+        <v>129758149</v>
       </c>
       <c r="B45" t="n">
-        <v>58114</v>
+        <v>57132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5466,17 +5462,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Stormyrbäcken, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>466857</v>
+        <v>466927</v>
       </c>
       <c r="R45" t="n">
-        <v>6858979</v>
+        <v>6859020</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5500,27 +5496,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Noterat läte.</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5535,22 +5516,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129175151</v>
+        <v>129175614</v>
       </c>
       <c r="B46" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5558,28 +5539,24 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -5590,10 +5567,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>466858</v>
+        <v>466857</v>
       </c>
       <c r="R46" t="n">
-        <v>6859162</v>
+        <v>6858979</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5625,7 +5602,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5635,7 +5612,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Noterat läte.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5662,7 +5644,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129281334</v>
+        <v>129175151</v>
       </c>
       <c r="B47" t="n">
         <v>58057</v>
@@ -5705,10 +5687,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>466961</v>
+        <v>466858</v>
       </c>
       <c r="R47" t="n">
-        <v>6859064</v>
+        <v>6859162</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5735,22 +5717,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5777,38 +5759,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129139476</v>
+        <v>129281334</v>
       </c>
       <c r="B48" t="n">
-        <v>99118</v>
+        <v>58057</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -5816,10 +5802,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>467031</v>
+        <v>466961</v>
       </c>
       <c r="R48" t="n">
-        <v>6858929</v>
+        <v>6859064</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5846,22 +5832,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5870,7 +5856,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5889,7 +5874,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129139492</v>
+        <v>129139476</v>
       </c>
       <c r="B49" t="n">
         <v>99118</v>
@@ -5917,16 +5902,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
@@ -5936,10 +5913,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>467077</v>
+        <v>467031</v>
       </c>
       <c r="R49" t="n">
-        <v>6858863</v>
+        <v>6858929</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6009,7 +5986,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129139507</v>
+        <v>129139492</v>
       </c>
       <c r="B50" t="n">
         <v>99118</v>
@@ -6039,7 +6016,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6056,10 +6033,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>467063</v>
+        <v>467077</v>
       </c>
       <c r="R50" t="n">
-        <v>6858862</v>
+        <v>6858863</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6129,7 +6106,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129139522</v>
+        <v>129139507</v>
       </c>
       <c r="B51" t="n">
         <v>99118</v>
@@ -6159,7 +6136,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6176,7 +6153,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>467078</v>
+        <v>467063</v>
       </c>
       <c r="R51" t="n">
         <v>6858862</v>
@@ -6249,7 +6226,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129139527</v>
+        <v>129139522</v>
       </c>
       <c r="B52" t="n">
         <v>99118</v>
@@ -6279,7 +6256,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6296,10 +6273,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>467072</v>
+        <v>467078</v>
       </c>
       <c r="R52" t="n">
-        <v>6858857</v>
+        <v>6858862</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6369,7 +6346,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129139538</v>
+        <v>129139527</v>
       </c>
       <c r="B53" t="n">
         <v>99118</v>
@@ -6397,8 +6374,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6408,10 +6393,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>467077</v>
+        <v>467072</v>
       </c>
       <c r="R53" t="n">
-        <v>6858856</v>
+        <v>6858857</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6481,7 +6466,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129139545</v>
+        <v>129139538</v>
       </c>
       <c r="B54" t="n">
         <v>99118</v>
@@ -6509,16 +6494,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
@@ -6528,10 +6505,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>467105</v>
+        <v>467077</v>
       </c>
       <c r="R54" t="n">
-        <v>6858853</v>
+        <v>6858856</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6601,7 +6578,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129174718</v>
+        <v>129139545</v>
       </c>
       <c r="B55" t="n">
         <v>99118</v>
@@ -6629,8 +6606,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -6640,10 +6625,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>467122</v>
+        <v>467105</v>
       </c>
       <c r="R55" t="n">
-        <v>6859101</v>
+        <v>6858853</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6670,22 +6655,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6713,7 +6698,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129174751</v>
+        <v>129174718</v>
       </c>
       <c r="B56" t="n">
         <v>99118</v>
@@ -6741,16 +6726,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -6760,10 +6737,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>467131</v>
+        <v>467122</v>
       </c>
       <c r="R56" t="n">
-        <v>6859085</v>
+        <v>6859101</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6833,7 +6810,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129174765</v>
+        <v>129174751</v>
       </c>
       <c r="B57" t="n">
         <v>99118</v>
@@ -6863,7 +6840,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -6880,10 +6857,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>467126</v>
+        <v>467131</v>
       </c>
       <c r="R57" t="n">
-        <v>6859081</v>
+        <v>6859085</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6953,7 +6930,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129174783</v>
+        <v>129174765</v>
       </c>
       <c r="B58" t="n">
         <v>99118</v>
@@ -6983,7 +6960,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7000,10 +6977,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>467141</v>
+        <v>467126</v>
       </c>
       <c r="R58" t="n">
-        <v>6859072</v>
+        <v>6859081</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7073,7 +7050,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129174795</v>
+        <v>129174783</v>
       </c>
       <c r="B59" t="n">
         <v>99118</v>
@@ -7120,10 +7097,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>467160</v>
+        <v>467141</v>
       </c>
       <c r="R59" t="n">
-        <v>6859063</v>
+        <v>6859072</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7193,7 +7170,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129174816</v>
+        <v>129174795</v>
       </c>
       <c r="B60" t="n">
         <v>99118</v>
@@ -7223,7 +7200,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7240,10 +7217,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>467156</v>
+        <v>467160</v>
       </c>
       <c r="R60" t="n">
-        <v>6859054</v>
+        <v>6859063</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7313,7 +7290,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129174832</v>
+        <v>129174816</v>
       </c>
       <c r="B61" t="n">
         <v>99118</v>
@@ -7343,7 +7320,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7360,10 +7337,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>467161</v>
+        <v>467156</v>
       </c>
       <c r="R61" t="n">
-        <v>6859044</v>
+        <v>6859054</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7433,7 +7410,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129174848</v>
+        <v>129174832</v>
       </c>
       <c r="B62" t="n">
         <v>99118</v>
@@ -7461,8 +7438,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7472,10 +7457,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>467183</v>
+        <v>467161</v>
       </c>
       <c r="R62" t="n">
-        <v>6859065</v>
+        <v>6859044</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7545,7 +7530,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129174865</v>
+        <v>129174848</v>
       </c>
       <c r="B63" t="n">
         <v>99118</v>
@@ -7573,16 +7558,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
@@ -7592,10 +7569,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>467191</v>
+        <v>467183</v>
       </c>
       <c r="R63" t="n">
-        <v>6859075</v>
+        <v>6859065</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7665,7 +7642,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129174881</v>
+        <v>129174865</v>
       </c>
       <c r="B64" t="n">
         <v>99118</v>
@@ -7695,7 +7672,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7712,10 +7689,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>467170</v>
+        <v>467191</v>
       </c>
       <c r="R64" t="n">
-        <v>6859051</v>
+        <v>6859075</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7785,7 +7762,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129174896</v>
+        <v>129174881</v>
       </c>
       <c r="B65" t="n">
         <v>99118</v>
@@ -7815,7 +7792,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7832,10 +7809,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>467147</v>
+        <v>467170</v>
       </c>
       <c r="R65" t="n">
-        <v>6859035</v>
+        <v>6859051</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7905,7 +7882,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129174912</v>
+        <v>129174896</v>
       </c>
       <c r="B66" t="n">
         <v>99118</v>
@@ -7935,7 +7912,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -7952,10 +7929,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>467130</v>
+        <v>467147</v>
       </c>
       <c r="R66" t="n">
-        <v>6859021</v>
+        <v>6859035</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8025,7 +8002,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129174925</v>
+        <v>129174912</v>
       </c>
       <c r="B67" t="n">
         <v>99118</v>
@@ -8053,8 +8030,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -8064,10 +8049,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>466878</v>
+        <v>467130</v>
       </c>
       <c r="R67" t="n">
-        <v>6858977</v>
+        <v>6859021</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8137,7 +8122,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129174937</v>
+        <v>129174925</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -8165,16 +8150,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -8184,10 +8161,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>466864</v>
+        <v>466878</v>
       </c>
       <c r="R68" t="n">
-        <v>6858963</v>
+        <v>6858977</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8257,7 +8234,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129803016</v>
+        <v>129174937</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -8287,22 +8264,30 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>140</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Silvestica2, knärot, Hjd</t>
+          <t>Stor-Svarttjärnen, Hjd</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>467100</v>
+        <v>466864</v>
       </c>
       <c r="R69" t="n">
-        <v>6859087</v>
+        <v>6858963</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8326,12 +8311,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8347,19 +8342,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129803017</v>
+        <v>129803016</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -8389,7 +8384,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>140</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8398,10 +8393,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>467115</v>
+        <v>467100</v>
       </c>
       <c r="R70" t="n">
-        <v>6859070</v>
+        <v>6859087</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
@@ -8461,7 +8456,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129803021</v>
+        <v>129803017</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -8489,17 +8484,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>467183</v>
+        <v>467115</v>
       </c>
       <c r="R71" t="n">
-        <v>6859085</v>
+        <v>6859070</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -8540,6 +8539,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8558,7 +8558,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129803022</v>
+        <v>129803021</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8593,10 +8593,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>466892</v>
+        <v>467183</v>
       </c>
       <c r="R72" t="n">
-        <v>6858962</v>
+        <v>6859085</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
@@ -8655,7 +8655,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129803023</v>
+        <v>129803022</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>466899</v>
+        <v>466892</v>
       </c>
       <c r="R73" t="n">
-        <v>6858960</v>
+        <v>6858962</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -8752,7 +8752,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129803025</v>
+        <v>129803023</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8787,10 +8787,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>466820</v>
+        <v>466899</v>
       </c>
       <c r="R74" t="n">
-        <v>6859174</v>
+        <v>6858960</v>
       </c>
       <c r="S74" t="n">
         <v>1</v>
@@ -8849,7 +8849,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129803026</v>
+        <v>129803025</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8884,10 +8884,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>467098</v>
+        <v>466820</v>
       </c>
       <c r="R75" t="n">
-        <v>6858924</v>
+        <v>6859174</v>
       </c>
       <c r="S75" t="n">
         <v>1</v>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129803027</v>
+        <v>129803026</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>467096</v>
+        <v>467098</v>
       </c>
       <c r="R76" t="n">
-        <v>6859052</v>
+        <v>6858924</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -9043,7 +9043,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129803028</v>
+        <v>129803027</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -9078,10 +9078,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>467092</v>
+        <v>467096</v>
       </c>
       <c r="R77" t="n">
-        <v>6859051</v>
+        <v>6859052</v>
       </c>
       <c r="S77" t="n">
         <v>1</v>
@@ -9140,7 +9140,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129803029</v>
+        <v>129803028</v>
       </c>
       <c r="B78" t="n">
         <v>99118</v>
@@ -9175,10 +9175,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>467101</v>
+        <v>467092</v>
       </c>
       <c r="R78" t="n">
-        <v>6859075</v>
+        <v>6859051</v>
       </c>
       <c r="S78" t="n">
         <v>1</v>
@@ -9237,7 +9237,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129803030</v>
+        <v>129803029</v>
       </c>
       <c r="B79" t="n">
         <v>99118</v>
@@ -9272,10 +9272,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>467112</v>
+        <v>467101</v>
       </c>
       <c r="R79" t="n">
-        <v>6859072</v>
+        <v>6859075</v>
       </c>
       <c r="S79" t="n">
         <v>1</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129803031</v>
+        <v>129803030</v>
       </c>
       <c r="B80" t="n">
         <v>99118</v>
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>467113</v>
+        <v>467112</v>
       </c>
       <c r="R80" t="n">
-        <v>6859065</v>
+        <v>6859072</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -9431,7 +9431,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129803032</v>
+        <v>129803031</v>
       </c>
       <c r="B81" t="n">
         <v>99118</v>
@@ -9466,10 +9466,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>467100</v>
+        <v>467113</v>
       </c>
       <c r="R81" t="n">
-        <v>6859092</v>
+        <v>6859065</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -9528,7 +9528,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129803033</v>
+        <v>129803032</v>
       </c>
       <c r="B82" t="n">
         <v>99118</v>
@@ -9563,10 +9563,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>467109</v>
+        <v>467100</v>
       </c>
       <c r="R82" t="n">
-        <v>6859093</v>
+        <v>6859092</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -9625,52 +9625,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129139418</v>
+        <v>129803033</v>
       </c>
       <c r="B83" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stor-Svarttjärnen, Hjd</t>
+          <t>Silvestica2, knärot, Hjd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>467036</v>
+        <v>467109</v>
       </c>
       <c r="R83" t="n">
-        <v>6858929</v>
+        <v>6859093</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9694,22 +9690,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>21:54</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9718,29 +9704,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129196629</v>
+        <v>129139418</v>
       </c>
       <c r="B84" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9748,16 +9733,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9776,10 +9761,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>466840</v>
+        <v>467036</v>
       </c>
       <c r="R84" t="n">
-        <v>6858994</v>
+        <v>6858929</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9806,22 +9791,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9849,37 +9834,38 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129139219</v>
+        <v>129196629</v>
       </c>
       <c r="B85" t="n">
-        <v>79085</v>
+        <v>97983</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9887,10 +9873,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>467080</v>
+        <v>466840</v>
       </c>
       <c r="R85" t="n">
-        <v>6859021</v>
+        <v>6858994</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9917,22 +9903,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>21:54</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9960,7 +9946,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129139232</v>
+        <v>129139219</v>
       </c>
       <c r="B86" t="n">
         <v>79085</v>
@@ -9998,10 +9984,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>467100</v>
+        <v>467080</v>
       </c>
       <c r="R86" t="n">
-        <v>6859013</v>
+        <v>6859021</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10071,7 +10057,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129175634</v>
+        <v>129139232</v>
       </c>
       <c r="B87" t="n">
         <v>79085</v>
@@ -10109,10 +10095,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>467082</v>
+        <v>467100</v>
       </c>
       <c r="R87" t="n">
-        <v>6859023</v>
+        <v>6859013</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10139,22 +10125,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10182,7 +10168,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129175650</v>
+        <v>129175634</v>
       </c>
       <c r="B88" t="n">
         <v>79085</v>
@@ -10220,10 +10206,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>466895</v>
+        <v>467082</v>
       </c>
       <c r="R88" t="n">
-        <v>6858952</v>
+        <v>6859023</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10293,7 +10279,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129175662</v>
+        <v>129175650</v>
       </c>
       <c r="B89" t="n">
         <v>79085</v>
@@ -10331,10 +10317,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>466918</v>
+        <v>466895</v>
       </c>
       <c r="R89" t="n">
-        <v>6858992</v>
+        <v>6858952</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10404,7 +10390,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129196390</v>
+        <v>129175662</v>
       </c>
       <c r="B90" t="n">
         <v>79085</v>
@@ -10442,10 +10428,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>467022</v>
+        <v>466918</v>
       </c>
       <c r="R90" t="n">
-        <v>6859109</v>
+        <v>6858992</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10515,7 +10501,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129196431</v>
+        <v>129196390</v>
       </c>
       <c r="B91" t="n">
         <v>79085</v>
@@ -10553,10 +10539,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>467059</v>
+        <v>467022</v>
       </c>
       <c r="R91" t="n">
-        <v>6859031</v>
+        <v>6859109</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10626,7 +10612,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129196497</v>
+        <v>129196431</v>
       </c>
       <c r="B92" t="n">
         <v>79085</v>
@@ -10664,10 +10650,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>466875</v>
+        <v>467059</v>
       </c>
       <c r="R92" t="n">
-        <v>6859133</v>
+        <v>6859031</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10737,7 +10723,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129196510</v>
+        <v>129196497</v>
       </c>
       <c r="B93" t="n">
         <v>79085</v>
@@ -10775,10 +10761,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>466862</v>
+        <v>466875</v>
       </c>
       <c r="R93" t="n">
-        <v>6859147</v>
+        <v>6859133</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10848,7 +10834,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129197157</v>
+        <v>129196510</v>
       </c>
       <c r="B94" t="n">
         <v>79085</v>
@@ -10886,10 +10872,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>466994</v>
+        <v>466862</v>
       </c>
       <c r="R94" t="n">
-        <v>6859246</v>
+        <v>6859147</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10959,7 +10945,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129197170</v>
+        <v>129197157</v>
       </c>
       <c r="B95" t="n">
         <v>79085</v>
@@ -10997,10 +10983,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>467020</v>
+        <v>466994</v>
       </c>
       <c r="R95" t="n">
-        <v>6859138</v>
+        <v>6859246</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11070,7 +11056,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129197181</v>
+        <v>129197170</v>
       </c>
       <c r="B96" t="n">
         <v>79085</v>
@@ -11108,10 +11094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>467027</v>
+        <v>467020</v>
       </c>
       <c r="R96" t="n">
-        <v>6859149</v>
+        <v>6859138</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11181,10 +11167,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129197427</v>
+        <v>129197181</v>
       </c>
       <c r="B97" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11192,21 +11178,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11219,10 +11205,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>467058</v>
+        <v>467027</v>
       </c>
       <c r="R97" t="n">
-        <v>6859193</v>
+        <v>6859149</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11249,22 +11235,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>21:36</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11292,7 +11278,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129197518</v>
+        <v>129197427</v>
       </c>
       <c r="B98" t="n">
         <v>79917</v>
@@ -11330,10 +11316,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>466892</v>
+        <v>467058</v>
       </c>
       <c r="R98" t="n">
-        <v>6859076</v>
+        <v>6859193</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11403,7 +11389,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129197561</v>
+        <v>129197518</v>
       </c>
       <c r="B99" t="n">
         <v>79917</v>
@@ -11441,10 +11427,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>466891</v>
+        <v>466892</v>
       </c>
       <c r="R99" t="n">
-        <v>6859119</v>
+        <v>6859076</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11511,6 +11497,117 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129197561</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Stor-Svarttjärnen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>466891</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6859119</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>21:36</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31892-2025 artfynd.xlsx
+++ b/artfynd/A 31892-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY100"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175183</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175199</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175206</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175713</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196589</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196771</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197373</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197410</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197281</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1901,6 +1956,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175597</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2020,6 +2080,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175792</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2139,6 +2204,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196314</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2258,6 +2328,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196342</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2377,6 +2452,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196354</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2474,6 +2554,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679931</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2585,6 +2670,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197604</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2696,6 +2786,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175708</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2807,6 +2902,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175673</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2918,6 +3018,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175680</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3029,6 +3134,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175685</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3140,6 +3250,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175691</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3251,6 +3366,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197207</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3362,6 +3482,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197264</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3473,6 +3598,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197648</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3570,6 +3700,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679926</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3667,6 +3802,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679929</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3764,6 +3904,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672969</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3865,6 +4010,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129138843</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3976,6 +4126,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196424</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4087,6 +4242,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196543</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4198,6 +4358,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196841</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4309,6 +4474,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197074</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4420,6 +4590,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197086</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4531,6 +4706,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197413</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4642,6 +4822,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175162</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4753,6 +4938,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197526</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4869,6 +5059,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4985,6 +5180,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175049</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5101,6 +5301,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175069</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5220,6 +5425,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175136</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5322,6 +5532,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679919</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5424,6 +5639,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129679923</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5525,6 +5745,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129758149</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5641,6 +5866,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175614</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5756,6 +5986,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175151</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5871,6 +6106,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281334</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5983,6 +6223,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139476</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6103,6 +6348,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139492</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6223,6 +6473,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139507</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6343,6 +6598,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139522</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6463,6 +6723,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139527</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6575,6 +6840,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139538</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6695,6 +6965,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139545</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6807,6 +7082,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174718</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6927,6 +7207,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174751</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7047,6 +7332,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174765</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7167,6 +7457,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174783</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7287,6 +7582,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174795</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7407,6 +7707,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174816</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7527,6 +7832,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174832</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7639,6 +7949,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174848</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7759,6 +8074,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174865</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7879,6 +8199,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174881</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7999,6 +8324,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174896</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8119,6 +8449,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174912</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8231,6 +8566,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174925</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8351,6 +8691,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129174937</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8453,6 +8798,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803016</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8555,6 +8905,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803017</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8652,6 +9007,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803021</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8749,6 +9109,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803022</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8846,6 +9211,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803023</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8943,6 +9313,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803025</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9040,6 +9415,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803026</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9137,6 +9517,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803027</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9234,6 +9619,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803028</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9331,6 +9721,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803029</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9428,6 +9823,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803030</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9525,6 +9925,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803031</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9622,6 +10027,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803032</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9719,6 +10129,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129803033</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9831,6 +10246,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139418</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9943,6 +10363,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196629</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10054,6 +10479,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139219</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10165,6 +10595,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129139232</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10276,6 +10711,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175634</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10387,6 +10827,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175650</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10498,6 +10943,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129175662</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10609,6 +11059,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196390</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10720,6 +11175,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196431</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10831,6 +11291,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196497</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10942,6 +11407,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129196510</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11053,6 +11523,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197157</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11164,6 +11639,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197170</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11275,6 +11755,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197181</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11386,6 +11871,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197427</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11497,6 +11987,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197518</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11608,8 +12103,114 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129197561</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>